--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -24672,7 +24672,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.DATE_SK</t>
+          <t>FACT_MEMBER_EVENT.DATE_SK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.MEMBER_DK</t>
+          <t>FACT_MEMBER_EVENT.MEMBER_DK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.EVENT_TYPE</t>
+          <t>FACT_MEMBER_EVENT.EVENT_TYPE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -24816,7 +24816,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.DVLP_DIV_CD</t>
+          <t>FACT_MEMBER_EVENT.DVLP_DIV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.DVLP_DIV_NM</t>
+          <t>FACT_MEMBER_EVENT.DVLP_DIV_NM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.SPNSR_AMT</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_AMT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.DEV_CNT</t>
+          <t>FACT_MEMBER_EVENT.DEV_CNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -25008,7 +25008,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.DEV_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.DEV_MEMBERS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_CNT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -25200,7 +25200,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_MEMBERS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.JOIN_DATE</t>
+          <t>FACT_MEMBER_EVENT.JOIN_DATE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_DATE</t>
+          <t>FACT_MEMBER_EVENT.STOP_DATE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -25344,7 +25344,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_REASON</t>
+          <t>FACT_MEMBER_EVENT.STOP_REASON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -25392,7 +25392,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_CHANNEL</t>
+          <t>FACT_MEMBER_EVENT.STOP_CHANNEL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_REASON_NM</t>
+          <t>FACT_MEMBER_EVENT.STOP_REASON_NM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_CHANNEL_NM</t>
+          <t>FACT_MEMBER_EVENT.STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -25536,7 +25536,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.NEW_EXISTING_FLAG</t>
+          <t>FACT_MEMBER_EVENT.NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.AGE_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.AGE_AT_EVENT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.AGE_BAND_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.AGE_BAND_AT_EVENT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.AREA_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.AREA_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.REGION_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CMPGN_CTGR_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_CTGR_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.MBER_INFLOW_PATH_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -27112,7 +27112,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CMPGN_TYPE1_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE1_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CMPGN_TYPE2_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE2_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -27208,7 +27208,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.MKTG_CMPGN_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -27256,7 +27256,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CMMN_BRND_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMMN_BRND_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -27304,7 +27304,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.MKTG_UTM_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.SPNSR_DIV_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -27400,7 +27400,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.SPNSR_DIV_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -27448,7 +27448,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CPR_DIV_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.CPR_DIV_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -544,12 +544,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 234,859/248,196 (94.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 22,452/248,196 (9.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 38,555/39,823 (96.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 34,057/39,823 (85.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,149/39,823 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 35,060/39,823 (88.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 16,420/39,823 (41.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 37,393/39,823 (93.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 37,612/39,823 (94.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 15,416/39,823 (38.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,739/39,823 (82.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,406/39,823 (91.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 34,241/39,823 (86.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 2,170/39,823 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 240/39,823 (0.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 38,597/39,823 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,823)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 2,100/39,823 (5.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 2,101/39,823 (5.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 14,641/39,823 (36.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CPC_SRC</t>
+          <t>CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.CPC_SRC</t>
+          <t>FACT_AD_BROADCAST.CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AGENCY_AD_BROADCAST.CPC_SRC</t>
+          <t>AGENCY_AD_BROADCAST.CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 18,661/39,823 (46.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 8,904/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 8,901/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 41,810,729/41,810,782 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 41,810,729/41,810,782 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 41,810,729/41,810,782 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 41,810,782/41,810,782 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 41,733,900/41,810,782 (99.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 41,161,967/41,810,782 (98.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2646,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 41,161,967/41,810,782 (98.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 41,810,782/41,810,782 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 41,613,494/41,810,782 (99.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 41,791,362/41,810,782 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 39,871,040/41,810,782 (95.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 41,161,966/41,810,782 (98.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,608,280/1,785,299 (90.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,785,298/1,785,299 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,785,299/1,785,299 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,785,299/1,785,299 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,784,805/1,785,299 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,784,805/1,785,299 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,606,883/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,606,883/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,606,887/1,606,887 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,606,883/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,606,883/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,606,883/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,606,886/1,606,887 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 1,606,887/1,606,887 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3622,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 1,606,887/1,606,887 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 1,606,887/1,606,887 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 1,606,887/1,606,887 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 1,595,474/1,606,887 (99.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 41,161,789/41,810,782 (98.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 39,861,514/41,810,782 (95.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 39,215,536/41,810,782 (93.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 3,622,269/41,810,782 (8.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 41,810,782/41,810,782 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 3,622,273/41,810,782 (8.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 41,508,701/41,508,842 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 41,508,701/41,508,842 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 41,508,701/41,508,842 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 41,508,842/41,508,842 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 2,025,238/41,508,842 (4.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 2,025,238/41,508,842 (4.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 992,491/41,508,842 (2.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4540,12 +4540,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 39,854,335/41,508,842 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4780,12 +4780,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,847,772/41,508,842 (88.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 37,676,363/41,508,842 (90.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 39,122,763/41,508,842 (94.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 36,800,958/41,508,842 (88.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 29,221/41,508,842 (0.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5308,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 642,805/41,508,842 (1.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 37,459,838/41,508,842 (90.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 38,579,737/41,508,842 (92.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5452,12 +5452,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5596,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5644,12 +5644,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6028,12 +6028,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,508,842) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,508,842)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 3,319,142/41,508,842 (8.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 3,426,155/41,508,842 (8.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6460,12 +6460,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 7,880,580/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 7,823,024/8,069,279 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6556,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 7,892,260/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 8,069,278/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 7,568,944/8,069,279 (93.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 7,568,944/8,069,279 (93.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6892,12 +6892,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 8,069,278/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 7,890,867/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 7,892,257/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>비영 8,069,275/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>비영 7,890,749/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7180,12 +7180,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>비영 1,598,977/8,069,279 (19.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7372,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7468,12 +7468,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 35,294/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7516,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>비영 7/7 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7804,12 +7804,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>전건 NULL (0/7)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>비영 5,884/5,885 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 41,969,590/41,969,590 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 41,969,590/41,969,590 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8218,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 41,969,590/41,969,590 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 25,417,305/41,969,590 (60.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 2,034,794/41,969,590 (4.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 490,811/41,969,590 (1.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8602,12 +8602,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8650,12 +8650,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8746,12 +8746,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8938,12 +8938,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -8986,12 +8986,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9034,12 +9034,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/41,969,590) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 39,959,503/41,969,590 (95.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9130,12 +9130,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 39,067,779/41,969,590 (93.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,969,590)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9226,12 +9226,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 41,969,590/41,969,590 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 21,689,115/41,969,590 (51.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9322,12 +9322,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 21,689,115/41,969,590 (51.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 29,311,615/41,969,590 (69.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9418,12 +9418,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 27,674,140/41,969,590 (65.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 27,674,140/41,969,590 (65.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,969,590)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9562,12 +9562,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 NULL (0/41,969,590)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9722,12 +9722,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9762,12 +9762,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,880,580/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,823,024/8,069,279 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10138,12 +10138,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 7,892,260/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10234,12 +10234,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,069,278/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10282,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10330,12 +10330,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 69/70 (98.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 70/70 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 69/70 (98.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10522,12 +10522,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 70/70 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 69/70 (98.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 70/70 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10666,12 +10666,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 9/11 (81.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10714,12 +10714,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 11/11 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10762,12 +10762,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11164,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11252,12 +11252,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11296,12 +11296,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11436,12 +11436,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11628,12 +11628,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11676,12 +11676,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11724,12 +11724,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11898,12 +11898,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 10,677/10,677 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 10,677/10,677 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 10,677/10,677 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 10,677/10,677 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 10,677/10,677 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12186,12 +12186,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12282,12 +12282,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12408,12 +12408,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 5,525/5,525 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12456,12 +12456,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 5,525/5,525 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12504,12 +12504,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12600,12 +12600,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 5,511/5,525 (99.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12648,12 +12648,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 5,441/5,525 (98.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 5,495/5,525 (99.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 5,483/5,525 (99.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,149/39,823 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12840,12 +12840,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 37,393/39,823 (93.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12888,12 +12888,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13016,12 +13016,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13144,12 +13144,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13270,12 +13270,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13318,12 +13318,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/248,196) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 179,123/248,196 (72.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13462,12 +13462,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/248,196) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13510,12 +13510,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13558,12 +13558,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 234,859/248,196 (94.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13606,12 +13606,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 199,322/248,196 (80.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13654,12 +13654,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 176,578/248,196 (71.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 22,452/248,196 (9.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 46,485/248,196 (18.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13798,12 +13798,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 13,415/248,196 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13846,12 +13846,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13894,12 +13894,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13942,12 +13942,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -13990,12 +13990,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 613/208,373 (0.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14038,12 +14038,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,048/208,373 (0.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14086,12 +14086,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,043/208,373 (0.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 87,640/208,373 (42.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14182,12 +14182,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 208,373/208,373 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14230,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 6,392/208,373 (3.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14278,12 +14278,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/208,373)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14326,12 +14326,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 42,034/208,373 (20.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 13,282/208,373 (6.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14422,12 +14422,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 3,400/208,373 (1.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14439,17 +14439,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CPC_SRC</t>
+          <t>CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_AD_DIGITAL.CPC_SRC</t>
+          <t>FACT_AD_DIGITAL.CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CPC_SRC</t>
+          <t>AGENCY_AD_DIGITAL.CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 13,924/208,373 (6.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14518,12 +14518,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 15,250/208,373 (7.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14566,12 +14566,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 3,896/208,373 (1.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 3,896/208,373 (1.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 6,392/208,373 (3.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14710,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 38,555/39,823 (96.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14758,12 +14758,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 34,057/39,823 (85.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14806,12 +14806,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,149/39,823 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14854,12 +14854,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 35,060/39,823 (88.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14902,12 +14902,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 16,420/39,823 (41.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14950,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -14998,12 +14998,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 37,393/39,823 (93.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15046,12 +15046,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 39,823/39,823 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15094,12 +15094,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 37,612/39,823 (94.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15142,12 +15142,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 15,416/39,823 (38.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15190,12 +15190,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,739/39,823 (82.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 36,406/39,823 (91.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15286,12 +15286,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 34,241/39,823 (86.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 2,170/39,823 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15382,12 +15382,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 240/39,823 (0.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 38,597/39,823 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/39,823)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 2,100/39,823 (5.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 2,101/39,823 (5.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15622,12 +15622,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 14,641/39,823 (36.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15639,17 +15639,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BRDC_CPC_SRC</t>
+          <t>CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FACT_AD_BROADCAST.CPC_SRC</t>
+          <t>FACT_AD_BROADCAST.CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AGENCY_AD_BROADCAST.CPC_SRC</t>
+          <t>AGENCY_AD_BROADCAST.CPC_CALL_SRC</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 18,661/39,823 (46.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15796,12 +15796,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 208,373/208,373 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15844,12 +15844,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15892,12 +15892,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15940,12 +15940,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 234,859/248,196 (94.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -15988,12 +15988,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 199,322/248,196 (80.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16036,12 +16036,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 176,578/248,196 (71.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16084,12 +16084,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 46,485/248,196 (18.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16132,12 +16132,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 13,415/248,196 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16180,12 +16180,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 613/208,373 (0.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16228,12 +16228,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 1,048/208,373 (0.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16276,12 +16276,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 1,043/208,373 (0.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16324,12 +16324,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 87,640/208,373 (42.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16372,12 +16372,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 208,373/208,373 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16420,12 +16420,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 6,392/208,373 (3.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16468,12 +16468,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 NULL (0/208,373)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16516,12 +16516,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 42,034/208,373 (20.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 13,282/208,373 (6.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16612,12 +16612,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 3,400/208,373 (1.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16629,17 +16629,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CPC_SRC</t>
+          <t>CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FACT_AD_DIGITAL.CPC_SRC</t>
+          <t>FACT_AD_DIGITAL.CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CPC_SRC</t>
+          <t>AGENCY_AD_DIGITAL.CPC_CLICK_SRC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16660,12 +16660,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 13,924/208,373 (6.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16708,12 +16708,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 15,250/208,373 (7.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16756,12 +16756,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 3,896/208,373 (1.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16804,12 +16804,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,896/208,373 (1.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16852,12 +16852,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 6,392/208,373 (3.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16892,12 +16892,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16932,12 +16932,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -16972,12 +16972,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17012,12 +17012,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17052,12 +17052,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17100,12 +17100,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17148,12 +17148,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 8,904/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17196,12 +17196,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 8,901/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17244,12 +17244,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 4/4 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17370,12 +17370,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17418,12 +17418,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17466,12 +17466,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 234,859/248,196 (94.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 199,322/248,196 (80.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17562,12 +17562,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 176,578/248,196 (71.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17610,12 +17610,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 22,452/248,196 (9.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 46,485/248,196 (18.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17706,12 +17706,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 13,415/248,196 (5.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17754,12 +17754,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17802,12 +17802,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17850,12 +17850,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 248,196/248,196 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17890,12 +17890,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17930,12 +17930,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -17970,12 +17970,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18010,12 +18010,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18050,12 +18050,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18098,12 +18098,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18146,12 +18146,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18194,12 +18194,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18242,12 +18242,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18290,12 +18290,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18338,12 +18338,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 35,294/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18386,12 +18386,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 8,905/8,905 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18434,12 +18434,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 8,904/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18482,12 +18482,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 8,904/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18530,12 +18530,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,905)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18578,12 +18578,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 8,901/8,905 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18626,12 +18626,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 5,301/8,905 (59.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18674,12 +18674,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,905)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18722,12 +18722,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 4/4 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18770,12 +18770,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 4/4 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18896,12 +18896,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18944,12 +18944,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -18992,12 +18992,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19040,12 +19040,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 9,213/160,166 (5.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19088,12 +19088,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19136,12 +19136,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 42,802/160,166 (26.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19184,12 +19184,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19232,12 +19232,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 148,646/160,166 (92.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 30,842/160,166 (19.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19328,12 +19328,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 65,409/160,166 (40.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19376,12 +19376,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 160,166/160,166 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/160,166)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/160,166)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19520,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 148,646/160,166 (92.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19568,12 +19568,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 146,992/160,166 (91.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19608,12 +19608,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19648,12 +19648,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19688,12 +19688,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19728,12 +19728,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19768,12 +19768,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19808,12 +19808,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19856,12 +19856,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,785,300/1,785,300 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19904,12 +19904,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,785,300/1,785,300 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,785,300)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 4,315/1,785,300 (0.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20048,12 +20048,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 7,861/7,862 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20096,12 +20096,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 7,852/7,862 (99.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20144,12 +20144,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 7,861/7,862 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20192,12 +20192,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 136/142 (95.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20240,12 +20240,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 136/142 (95.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20288,12 +20288,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 141/142 (99.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20336,12 +20336,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 141/142 (99.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20384,12 +20384,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 141/142 (99.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20432,12 +20432,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 4/4 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20480,12 +20480,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20528,12 +20528,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20576,12 +20576,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20702,12 +20702,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20750,12 +20750,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20798,12 +20798,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,332/1,332 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20846,12 +20846,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 274/1,332 (20.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20894,12 +20894,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 344/1,332 (25.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20942,12 +20942,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -20990,12 +20990,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21038,12 +21038,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,332)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21086,12 +21086,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21134,12 +21134,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21182,12 +21182,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21230,12 +21230,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21278,12 +21278,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 180/180 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21326,12 +21326,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 179/180 (99.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21374,12 +21374,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21422,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21470,12 +21470,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21518,12 +21518,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21566,12 +21566,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21692,12 +21692,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,095,887/1,258,775 (87.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21740,12 +21740,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21788,12 +21788,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21836,12 +21836,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 106,512/1,258,775 (8.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21884,12 +21884,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 3,495/1,258,775 (0.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21932,12 +21932,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,258,775) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -21980,12 +21980,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22028,12 +22028,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,961/1,258,775 (0.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22076,12 +22076,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22124,12 +22124,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,258,775) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22172,12 +22172,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,258,775) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22220,12 +22220,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,258,775) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22268,12 +22268,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,258,775) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22316,12 +22316,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 4,847/1,258,775 (0.4%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22364,12 +22364,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 12,979/1,258,775 (1.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22412,12 +22412,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,258,775)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22460,12 +22460,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,247,535/1,258,775 (99.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22508,12 +22508,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,249,090/1,258,775 (99.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22556,12 +22556,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,095,810/1,258,775 (87.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22604,12 +22604,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,247,535/1,258,775 (99.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22652,12 +22652,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,247,533/1,258,775 (99.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22700,12 +22700,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,249,090/1,258,775 (99.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22748,12 +22748,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,249,088/1,258,775 (99.2%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22796,12 +22796,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,095,810/1,258,775 (87.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22844,12 +22844,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,095,808/1,258,775 (87.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22892,12 +22892,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22940,12 +22940,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -22988,12 +22988,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23036,12 +23036,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,258,775/1,258,775 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23076,12 +23076,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23116,12 +23116,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23156,12 +23156,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23196,12 +23196,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23236,12 +23236,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23276,12 +23276,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23324,12 +23324,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23372,12 +23372,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23420,12 +23420,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23468,12 +23468,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,880,580/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23516,12 +23516,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,823,024/8,069,279 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23564,12 +23564,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23612,12 +23612,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23660,12 +23660,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,892,260/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23708,12 +23708,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 8,069,278/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23756,12 +23756,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23804,12 +23804,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23852,12 +23852,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,937/3,937 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23900,12 +23900,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 3,936/3,937 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23948,12 +23948,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 3,937/3,937 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -23996,12 +23996,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 3,936/3,937 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 3,936/3,937 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24092,12 +24092,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 3,936/3,937 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24140,12 +24140,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 3,936/3,937 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24188,12 +24188,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,935/3,937 (99.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24236,12 +24236,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 3,935/3,937 (99.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24284,12 +24284,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,937)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24332,12 +24332,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 3,491/3,937 (88.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24428,12 +24428,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24476,12 +24476,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24524,12 +24524,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24572,12 +24572,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24698,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 4,716,270/4,716,360 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24746,12 +24746,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 4,716,360/4,716,360 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24794,12 +24794,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 4,716,360/4,716,360 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24842,12 +24842,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 3,654,929/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 3,654,929/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24938,12 +24938,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 3,654,878/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -24986,12 +24986,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 2,325,729/4,716,360 (49.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25034,12 +25034,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,325,729/4,716,360 (49.3%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25082,12 +25082,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25130,12 +25130,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25178,12 +25178,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/4,716,360) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25226,12 +25226,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/4,716,360) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 3,654,929/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25322,12 +25322,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25370,12 +25370,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25418,12 +25418,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25466,12 +25466,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25514,12 +25514,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,061,431/4,716,360 (22.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25562,12 +25562,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 NULL (0/4,716,360)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25610,12 +25610,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 3,654,929/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25658,12 +25658,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 3,654,929/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25706,12 +25706,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,654,923/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25754,12 +25754,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 3,634,251/4,716,360 (77.1%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25794,12 +25794,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25834,12 +25834,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25874,12 +25874,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25914,12 +25914,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 16,437/16,437 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25954,12 +25954,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -25994,12 +25994,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26034,12 +26034,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26082,12 +26082,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26130,12 +26130,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26178,12 +26178,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 8,068,785/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26226,12 +26226,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 7,880,580/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26274,12 +26274,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,823,024/8,069,279 (96.9%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26322,12 +26322,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26370,12 +26370,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 7,880,585/8,069,279 (97.7%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26418,12 +26418,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,892,260/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26466,12 +26466,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 8,069,278/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26514,12 +26514,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,568,944/8,069,279 (93.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26562,12 +26562,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,568,944/8,069,279 (93.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26610,12 +26610,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26658,12 +26658,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 8,069,279/8,069,279 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26706,12 +26706,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,892,257/8,069,279 (97.8%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26754,12 +26754,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 8,069,275/8,069,279 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26802,12 +26802,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26850,12 +26850,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26898,12 +26898,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26946,12 +26946,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 36,769/36,769 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 35,298/36,769 (96.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27042,12 +27042,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27090,12 +27090,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27138,12 +27138,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27186,12 +27186,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27234,12 +27234,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27282,12 +27282,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27330,12 +27330,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 875,683/4,716,360 (18.6%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27378,12 +27378,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27426,12 +27426,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27474,12 +27474,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27522,12 +27522,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 3,654,911/4,716,360 (77.5%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27570,12 +27570,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27618,12 +27618,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27666,12 +27666,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27714,12 +27714,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27762,12 +27762,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27810,12 +27810,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27858,12 +27858,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27906,12 +27906,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -27954,12 +27954,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -28002,12 +28002,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>
@@ -28050,12 +28050,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>비영 5,884/5,885 (100.0%)</t>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -544,12 +544,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 48,457/48,457 (100%)</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 58,678/77,505 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 21,459/77,505 (27.7%)</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 37,106/48,457 (76.6%)</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,718/48,457 (67.5%)</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,104/48,457 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 33,721/48,457 (69.6%)</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 15,993/48,457 (33.0%)</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 45,121/48,457 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,009/48,457 (74.3%)</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 48,457/48,457 (100%)</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 42,618/48,457 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 14,990/48,457 (30.9%)</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,933/48,457 (68.0%)</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,002/48,457 (72.2%)</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,902/48,457 (67.9%)</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 45,974/48,457 (94.9%)</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,104/48,457 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,943/48,457 (74.2%)</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/48,457)</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,953/48,457 (16.4%)</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,953/48,457 (16.4%)</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 13,971/48,457 (28.8%)</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 17,801/48,457 (36.7%)</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,366/3,367 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,357/3,367 (99.7%)</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,732/41,810,782 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,732/41,810,782 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,732/41,810,782 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,782/41,810,782 (100%)</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,733,900/41,810,782 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,161,967/41,810,782 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2646,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,161,967/41,810,782 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,782/41,810,782 (100%)</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,613,494/41,810,782 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,791,362/41,810,782 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,871,043/41,810,782 (95.4%)</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,161,966/41,810,782 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,608,280/1,785,299 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,785,298/1,785,299 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,785,299/1,785,299 (100%)</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,785,299/1,785,299 (100%)</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,784,805/1,785,299 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,784,805/1,785,299 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,867/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,867/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,871/1,606,871 (100%)</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,867/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,867/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,867/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,870/1,606,871 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,871/1,606,871 (100%)</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3622,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,871/1,606,871 (100%)</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,871/1,606,871 (100%)</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,606,871/1,606,871 (100%)</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,595,458/1,606,871 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,161,789/41,810,782 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,861,514/41,810,782 (95.3%)</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,215,536/41,810,782 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,622,269/41,810,782 (8.7%)</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,810,782/41,810,782 (100%)</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,622,273/41,810,782 (8.7%)</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,686/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,686/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,686/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,824/41,508,824 (100%)</t>
         </is>
       </c>
     </row>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,025,221/41,508,824 (4.9%)</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,025,221/41,508,824 (4.9%)</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 992,490/41,508,824 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -4487,17 +4487,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,381,518/41,508,824 (8.1%)</t>
         </is>
       </c>
     </row>
@@ -4540,12 +4540,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,854,330/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4631,17 +4631,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 40,335,569/41,508,824 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -4679,17 +4679,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 40,335,577/41,508,824 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -4727,17 +4727,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,840,830/41,508,824 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -4775,17 +4775,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,840,830/41,508,824 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 115,399/41,508,824 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,227,134/41,508,824 (3.0%)</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,847,772/41,508,824 (88.8%)</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 37,676,358/41,508,824 (90.8%)</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,122,763/41,508,824 (94.3%)</t>
         </is>
       </c>
     </row>
@@ -5116,12 +5116,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,508,824) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,426,155/41,508,824 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5212,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,800,958/41,508,824 (88.7%)</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,221/41,508,824 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5308,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 642,805/41,508,824 (1.5%)</t>
         </is>
       </c>
     </row>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 37,459,838/41,508,824 (90.2%)</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 38,579,737/41,508,824 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -5452,12 +5452,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,508,824) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,508,824) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,024,620/41,508,824 (4.9%)</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5596,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,477,398/41,508,824 (10.8%)</t>
         </is>
       </c>
     </row>
@@ -5644,12 +5644,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 306,788/41,508,824 (0.7%)</t>
         </is>
       </c>
     </row>
@@ -5692,12 +5692,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 114,466/41,508,824 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -5735,17 +5735,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,682/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5767,12 +5767,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.SPNSR_DSCNTC_DE</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -5783,17 +5783,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,017,613/41,508,824 (7.3%)</t>
         </is>
       </c>
     </row>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,682/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,682/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,730,533/41,508,824 (95.7%)</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 34,222,528/41,508,824 (82.4%)</t>
         </is>
       </c>
     </row>
@@ -6103,12 +6103,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -6119,17 +6119,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 38,621,693/41,508,824 (93.0%)</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6151,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH_NM</t>
+          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,508,682/41,508,824 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,319,142/41,508,824 (8.0%)</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,426,155/41,508,824 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6460,12 +6460,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,580/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,823,024/8,069,279 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6556,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,260/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,278/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,568,944/8,069,279 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,568,944/8,069,279 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -6892,12 +6892,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,278/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,890,867/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,257/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,275/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,890,749/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -7180,12 +7180,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,598,977/8,069,279 (19.8%)</t>
         </is>
       </c>
     </row>
@@ -7228,12 +7228,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7372,12 +7372,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7468,12 +7468,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,294/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7516,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7660,12 +7660,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7/7 (100%)</t>
         </is>
       </c>
     </row>
@@ -7804,12 +7804,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/7)</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,885/5,885 (100%)</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,885/5,885 (100%)</t>
         </is>
       </c>
     </row>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,884/5,885 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -8122,12 +8122,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,935,344/41,935,344 (100%)</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,935,344/41,935,344 (100%)</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8218,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,935,344/41,935,344 (100%)</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 25,384,521/41,935,344 (60.5%)</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,034,467/41,935,344 (4.9%)</t>
         </is>
       </c>
     </row>
@@ -8341,12 +8341,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 490,762/41,935,344 (1.2%)</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -8410,12 +8410,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,935,344) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8437,12 +8437,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,935,344) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8485,12 +8485,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,935,344) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8533,12 +8533,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/41,935,344) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -8602,12 +8602,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 52,657/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -8650,12 +8650,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 52,407/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 34,332/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -8746,12 +8746,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 34,106/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -8794,12 +8794,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 30,696/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 30,187/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8869,12 +8869,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 157,097/41,935,344 (0.4%)</t>
         </is>
       </c>
     </row>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -8938,12 +8938,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 70,027/41,935,344 (0.2%)</t>
         </is>
       </c>
     </row>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8986,12 +8986,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 611,684/41,935,344 (1.5%)</t>
         </is>
       </c>
     </row>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -9034,12 +9034,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 601,858/41,935,344 (1.4%)</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,925,364/41,935,344 (95.2%)</t>
         </is>
       </c>
     </row>
@@ -9130,12 +9130,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 39,033,873/41,935,344 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/41,935,344)</t>
         </is>
       </c>
     </row>
@@ -9226,12 +9226,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 41,935,344/41,935,344 (100%)</t>
         </is>
       </c>
     </row>
@@ -9274,12 +9274,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 21,671,318/41,935,344 (51.7%)</t>
         </is>
       </c>
     </row>
@@ -9322,12 +9322,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 21,671,318/41,935,344 (51.7%)</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,294,521/41,935,344 (69.9%)</t>
         </is>
       </c>
     </row>
@@ -9418,12 +9418,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 27,657,076/41,935,344 (66.0%)</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 27,657,076/41,935,344 (66.0%)</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9514,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/41,935,344)</t>
         </is>
       </c>
     </row>
@@ -9562,12 +9562,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/41,935,344)</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9682,12 +9682,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9722,12 +9722,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -9762,12 +9762,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9994,12 +9994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,580/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,823,024/8,069,279 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -10138,12 +10138,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -10186,12 +10186,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,260/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -10234,12 +10234,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,278/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -10282,12 +10282,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -10330,12 +10330,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 69/70 (98.6%)</t>
         </is>
       </c>
     </row>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 70/70 (100%)</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 69/70 (98.6%)</t>
         </is>
       </c>
     </row>
@@ -10522,12 +10522,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 70/70 (100%)</t>
         </is>
       </c>
     </row>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 69/70 (98.6%)</t>
         </is>
       </c>
     </row>
@@ -10618,12 +10618,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 70/70 (100%)</t>
         </is>
       </c>
     </row>
@@ -10666,12 +10666,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 9/11 (81.8%)</t>
         </is>
       </c>
     </row>
@@ -10714,12 +10714,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 11/11 (100%)</t>
         </is>
       </c>
     </row>
@@ -10762,12 +10762,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10906,12 +10906,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11164,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11208,12 +11208,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11252,12 +11252,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11296,12 +11296,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11340,12 +11340,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -11436,12 +11436,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -11484,12 +11484,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -11628,12 +11628,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -11676,12 +11676,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -11724,12 +11724,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -11898,12 +11898,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 10,677/10,677 (100%)</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 10,677/10,677 (100%)</t>
         </is>
       </c>
     </row>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 10,677/10,677 (100%)</t>
         </is>
       </c>
     </row>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 10,677/10,677 (100%)</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12090,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 10,677/10,677 (100%)</t>
         </is>
       </c>
     </row>
@@ -12138,12 +12138,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -12186,12 +12186,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -12234,12 +12234,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -12282,12 +12282,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -12408,12 +12408,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12456,12 +12456,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12504,12 +12504,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -12600,12 +12600,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12648,12 +12648,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12696,12 +12696,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12744,12 +12744,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_AD_BROADCAST_CASE` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -12792,12 +12792,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,104/48,457 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -12840,12 +12840,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,009/48,457 (74.3%)</t>
         </is>
       </c>
     </row>
@@ -12888,12 +12888,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 48,457/48,457 (100%)</t>
         </is>
       </c>
     </row>
@@ -12936,12 +12936,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 45,121/48,457 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -13016,12 +13016,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -13144,12 +13144,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -13270,12 +13270,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -13318,12 +13318,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/77,505) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 19,952/77,505 (25.7%)</t>
         </is>
       </c>
     </row>
@@ -13462,12 +13462,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/77,505) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13510,12 +13510,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 48,457/77,505 (62.5%)</t>
         </is>
       </c>
     </row>
@@ -13558,12 +13558,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 58,678/77,505 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -13606,12 +13606,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 23,255/77,505 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -13654,12 +13654,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 25,148/77,505 (32.4%)</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 21,459/77,505 (27.7%)</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -13798,12 +13798,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -13846,12 +13846,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -13894,12 +13894,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -13942,12 +13942,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -13990,12 +13990,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,025/29,048 (3.5%)</t>
         </is>
       </c>
     </row>
@@ -14038,12 +14038,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,904/29,048 (10.0%)</t>
         </is>
       </c>
     </row>
@@ -14086,12 +14086,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,048/29,048 (100%)</t>
         </is>
       </c>
     </row>
@@ -14182,12 +14182,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,048/29,048 (100%)</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14230,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,392/29,048 (22.0%)</t>
         </is>
       </c>
     </row>
@@ -14278,12 +14278,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -14326,12 +14326,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 15,893/29,048 (54.7%)</t>
         </is>
       </c>
     </row>
@@ -14422,12 +14422,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,226/29,048 (14.5%)</t>
         </is>
       </c>
     </row>
@@ -14470,12 +14470,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 18,563/29,048 (63.9%)</t>
         </is>
       </c>
     </row>
@@ -14518,12 +14518,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 20,064/29,048 (69.1%)</t>
         </is>
       </c>
     </row>
@@ -14566,12 +14566,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,226/29,048 (21.4%)</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,226/29,048 (21.4%)</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,392/29,048 (22.0%)</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14710,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 37,106/48,457 (76.6%)</t>
         </is>
       </c>
     </row>
@@ -14758,12 +14758,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,718/48,457 (67.5%)</t>
         </is>
       </c>
     </row>
@@ -14806,12 +14806,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,104/48,457 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -14854,12 +14854,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 33,721/48,457 (69.6%)</t>
         </is>
       </c>
     </row>
@@ -14902,12 +14902,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 15,993/48,457 (33.0%)</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14950,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 45,121/48,457 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -14998,12 +14998,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,009/48,457 (74.3%)</t>
         </is>
       </c>
     </row>
@@ -15046,12 +15046,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 48,457/48,457 (100%)</t>
         </is>
       </c>
     </row>
@@ -15094,12 +15094,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 42,618/48,457 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -15142,12 +15142,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 14,990/48,457 (30.9%)</t>
         </is>
       </c>
     </row>
@@ -15190,12 +15190,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,933/48,457 (68.0%)</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15238,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,002/48,457 (72.2%)</t>
         </is>
       </c>
     </row>
@@ -15286,12 +15286,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 32,902/48,457 (67.9%)</t>
         </is>
       </c>
     </row>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 45,974/48,457 (94.9%)</t>
         </is>
       </c>
     </row>
@@ -15382,12 +15382,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,104/48,457 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -15430,12 +15430,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,943/48,457 (74.2%)</t>
         </is>
       </c>
     </row>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/48,457)</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,953/48,457 (16.4%)</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,953/48,457 (16.4%)</t>
         </is>
       </c>
     </row>
@@ -15622,12 +15622,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 13,971/48,457 (28.8%)</t>
         </is>
       </c>
     </row>
@@ -15670,12 +15670,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 17,801/48,457 (36.7%)</t>
         </is>
       </c>
     </row>
@@ -15796,12 +15796,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,048/29,048 (100%)</t>
         </is>
       </c>
     </row>
@@ -15844,12 +15844,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -15892,12 +15892,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -15940,12 +15940,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 58,678/77,505 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -15988,12 +15988,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 23,255/77,505 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -16036,12 +16036,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 25,148/77,505 (32.4%)</t>
         </is>
       </c>
     </row>
@@ -16084,12 +16084,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -16132,12 +16132,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -16180,12 +16180,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,025/29,048 (3.5%)</t>
         </is>
       </c>
     </row>
@@ -16228,12 +16228,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,904/29,048 (10.0%)</t>
         </is>
       </c>
     </row>
@@ -16276,12 +16276,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -16324,12 +16324,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,048/29,048 (100%)</t>
         </is>
       </c>
     </row>
@@ -16372,12 +16372,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 29,048/29,048 (100%)</t>
         </is>
       </c>
     </row>
@@ -16420,12 +16420,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,392/29,048 (22.0%)</t>
         </is>
       </c>
     </row>
@@ -16468,12 +16468,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -16516,12 +16516,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/29,048)</t>
         </is>
       </c>
     </row>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 15,893/29,048 (54.7%)</t>
         </is>
       </c>
     </row>
@@ -16612,12 +16612,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,226/29,048 (14.5%)</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 18,563/29,048 (63.9%)</t>
         </is>
       </c>
     </row>
@@ -16708,12 +16708,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 20,064/29,048 (69.1%)</t>
         </is>
       </c>
     </row>
@@ -16756,12 +16756,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,226/29,048 (21.4%)</t>
         </is>
       </c>
     </row>
@@ -16804,12 +16804,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,226/29,048 (21.4%)</t>
         </is>
       </c>
     </row>
@@ -16852,12 +16852,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 6,392/29,048 (22.0%)</t>
         </is>
       </c>
     </row>
@@ -16892,12 +16892,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -16932,12 +16932,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -16972,12 +16972,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17012,12 +17012,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17052,12 +17052,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -17100,12 +17100,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -17148,12 +17148,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,366/3,367 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17196,12 +17196,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,357/3,367 (99.7%)</t>
         </is>
       </c>
     </row>
@@ -17244,12 +17244,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2/2 (100%)</t>
         </is>
       </c>
     </row>
@@ -17370,12 +17370,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17418,12 +17418,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17466,12 +17466,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 58,678/77,505 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 23,255/77,505 (30.0%)</t>
         </is>
       </c>
     </row>
@@ -17562,12 +17562,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 25,148/77,505 (32.4%)</t>
         </is>
       </c>
     </row>
@@ -17610,12 +17610,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 21,459/77,505 (27.7%)</t>
         </is>
       </c>
     </row>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -17706,12 +17706,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,139/77,505 (9.2%)</t>
         </is>
       </c>
     </row>
@@ -17754,12 +17754,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17802,12 +17802,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17850,12 +17850,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17890,12 +17890,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -17930,12 +17930,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17970,12 +17970,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18010,12 +18010,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18050,12 +18050,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -18098,12 +18098,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -18146,12 +18146,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18194,12 +18194,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18242,12 +18242,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -18290,12 +18290,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18338,12 +18338,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,294/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18386,12 +18386,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,367/3,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -18434,12 +18434,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,366/3,367 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18482,12 +18482,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,366/3,367 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18530,12 +18530,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/3,367)</t>
         </is>
       </c>
     </row>
@@ -18578,12 +18578,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,357/3,367 (99.7%)</t>
         </is>
       </c>
     </row>
@@ -18626,12 +18626,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,366/3,367 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18674,12 +18674,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/3,367)</t>
         </is>
       </c>
     </row>
@@ -18722,12 +18722,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2/2 (100%)</t>
         </is>
       </c>
     </row>
@@ -18770,12 +18770,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2/2 (100%)</t>
         </is>
       </c>
     </row>
@@ -18896,12 +18896,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -18944,12 +18944,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -18992,12 +18992,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19040,12 +19040,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19088,12 +19088,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19136,12 +19136,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19184,12 +19184,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19232,12 +19232,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19280,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19328,12 +19328,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19376,12 +19376,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19520,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19568,12 +19568,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
         </is>
       </c>
     </row>
@@ -19608,12 +19608,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -19648,12 +19648,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -19688,12 +19688,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -19728,12 +19728,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -19768,12 +19768,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -19808,12 +19808,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -19856,12 +19856,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,785,300/1,785,300 (100%)</t>
         </is>
       </c>
     </row>
@@ -19904,12 +19904,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,785,300/1,785,300 (100%)</t>
         </is>
       </c>
     </row>
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,785,300)</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,785,300)</t>
         </is>
       </c>
     </row>
@@ -20048,12 +20048,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1/1 (100%)</t>
         </is>
       </c>
     </row>
@@ -20096,12 +20096,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1/1 (100%)</t>
         </is>
       </c>
     </row>
@@ -20144,12 +20144,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1/1 (100%)</t>
         </is>
       </c>
     </row>
@@ -20192,12 +20192,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1/1 (100%)</t>
         </is>
       </c>
     </row>
@@ -20240,12 +20240,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1/1 (100%)</t>
         </is>
       </c>
     </row>
@@ -20288,12 +20288,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1)</t>
         </is>
       </c>
     </row>
@@ -20336,12 +20336,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1)</t>
         </is>
       </c>
     </row>
@@ -20384,12 +20384,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1)</t>
         </is>
       </c>
     </row>
@@ -20432,12 +20432,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2/2 (100%)</t>
         </is>
       </c>
     </row>
@@ -20480,12 +20480,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -20528,12 +20528,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -20576,12 +20576,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -20702,12 +20702,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -20750,12 +20750,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -20798,12 +20798,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -20846,12 +20846,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 274/1,332 (20.6%)</t>
         </is>
       </c>
     </row>
@@ -20894,12 +20894,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 344/1,332 (25.8%)</t>
         </is>
       </c>
     </row>
@@ -20942,12 +20942,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -20990,12 +20990,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -21038,12 +21038,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -21086,12 +21086,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -21134,12 +21134,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -21182,12 +21182,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -21230,12 +21230,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -21278,12 +21278,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 180/180 (100%)</t>
         </is>
       </c>
     </row>
@@ -21326,12 +21326,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 179/180 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -21374,12 +21374,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21422,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -21470,12 +21470,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -21518,12 +21518,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -21566,12 +21566,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -21692,12 +21692,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,677/1,248,727 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21740,12 +21740,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -21788,12 +21788,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -21836,12 +21836,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 106,503/1,248,727 (8.5%)</t>
         </is>
       </c>
     </row>
@@ -21884,12 +21884,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,495/1,248,727 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -21932,12 +21932,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 52,826/1,248,727 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -21980,12 +21980,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -22028,12 +22028,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,961/1,248,727 (0.2%)</t>
         </is>
       </c>
     </row>
@@ -22076,12 +22076,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -22124,12 +22124,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,214,961/1,248,727 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 130,137/1,248,727 (10.4%)</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -22220,12 +22220,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 17,118/1,248,727 (1.4%)</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -22268,12 +22268,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -22316,12 +22316,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,842/1,248,727 (0.4%)</t>
         </is>
       </c>
     </row>
@@ -22364,12 +22364,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 12,979/1,248,727 (1.0%)</t>
         </is>
       </c>
     </row>
@@ -22412,12 +22412,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,248,727)</t>
         </is>
       </c>
     </row>
@@ -22460,12 +22460,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,237,489/1,248,727 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -22508,12 +22508,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,239,045/1,248,727 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -22556,12 +22556,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,085,796/1,248,727 (87.0%)</t>
         </is>
       </c>
     </row>
@@ -22604,12 +22604,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,237,489/1,248,727 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -22652,12 +22652,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,237,487/1,248,727 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -22700,12 +22700,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,239,045/1,248,727 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -22748,12 +22748,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,239,043/1,248,727 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -22796,12 +22796,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,085,796/1,248,727 (87.0%)</t>
         </is>
       </c>
     </row>
@@ -22844,12 +22844,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,085,794/1,248,727 (87.0%)</t>
         </is>
       </c>
     </row>
@@ -22892,12 +22892,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -22940,12 +22940,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -22988,12 +22988,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -23036,12 +23036,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,248,727/1,248,727 (100%)</t>
         </is>
       </c>
     </row>
@@ -23076,12 +23076,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -23116,12 +23116,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23156,12 +23156,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23196,12 +23196,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -23236,12 +23236,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23276,12 +23276,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -23324,12 +23324,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23372,12 +23372,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23420,12 +23420,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23468,12 +23468,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,580/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -23516,12 +23516,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,823,024/8,069,279 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -23564,12 +23564,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -23612,12 +23612,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -23660,12 +23660,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,260/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -23708,12 +23708,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,278/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23756,12 +23756,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -23804,12 +23804,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -23852,12 +23852,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,937/3,937 (100%)</t>
         </is>
       </c>
     </row>
@@ -23900,12 +23900,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,936/3,937 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23948,12 +23948,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,937/3,937 (100%)</t>
         </is>
       </c>
     </row>
@@ -23996,12 +23996,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,936/3,937 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,936/3,937 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -24092,12 +24092,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,936/3,937 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -24140,12 +24140,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,936/3,937 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -24188,12 +24188,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,935/3,937 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24236,12 +24236,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,935/3,937 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24284,12 +24284,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/3,937)</t>
         </is>
       </c>
     </row>
@@ -24332,12 +24332,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,491/3,937 (88.7%)</t>
         </is>
       </c>
     </row>
@@ -24380,12 +24380,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -24428,12 +24428,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -24476,12 +24476,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -24524,12 +24524,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -24572,12 +24572,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24698,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,715,998/4,716,088 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -24746,12 +24746,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,716,088/4,716,088 (100%)</t>
         </is>
       </c>
     </row>
@@ -24773,12 +24773,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.MBER_NO</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -24794,12 +24794,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,716,088/4,716,088 (100%)</t>
         </is>
       </c>
     </row>
@@ -24842,12 +24842,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,658/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,658/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -24938,12 +24938,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,607/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -24986,12 +24986,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,325,458/4,716,088 (49.3%)</t>
         </is>
       </c>
     </row>
@@ -25034,12 +25034,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 2,325,458/4,716,088 (49.3%)</t>
         </is>
       </c>
     </row>
@@ -25082,12 +25082,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25130,12 +25130,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25178,12 +25178,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 389,010/4,716,088 (8.2%)</t>
         </is>
       </c>
     </row>
@@ -25226,12 +25226,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 389,010/4,716,088 (8.2%)</t>
         </is>
       </c>
     </row>
@@ -25274,12 +25274,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,658/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -25322,12 +25322,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25370,12 +25370,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25418,12 +25418,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25466,12 +25466,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25514,12 +25514,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,061,430/4,716,088 (22.5%)</t>
         </is>
       </c>
     </row>
@@ -25541,12 +25541,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH_NM</t>
+          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -25562,12 +25562,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 4,716,088/4,716,088 (100%)</t>
         </is>
       </c>
     </row>
@@ -25610,12 +25610,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,658/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -25658,12 +25658,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,658/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -25706,12 +25706,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,652/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -25754,12 +25754,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,633,980/4,716,088 (77.1%)</t>
         </is>
       </c>
     </row>
@@ -25794,12 +25794,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -25834,12 +25834,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -25874,12 +25874,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -25914,12 +25914,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -25954,12 +25954,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -25994,12 +25994,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26034,12 +26034,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -26082,12 +26082,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26130,12 +26130,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26178,12 +26178,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,068,785/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26226,12 +26226,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,580/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -26274,12 +26274,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,823,024/8,069,279 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -26322,12 +26322,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -26370,12 +26370,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,880,585/8,069,279 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -26418,12 +26418,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,260/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -26466,12 +26466,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,278/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26514,12 +26514,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,568,944/8,069,279 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -26562,12 +26562,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,568,944/8,069,279 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -26610,12 +26610,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -26658,12 +26658,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,279/8,069,279 (100%)</t>
         </is>
       </c>
     </row>
@@ -26706,12 +26706,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 7,892,257/8,069,279 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -26754,12 +26754,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 8,069,275/8,069,279 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26802,12 +26802,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -26850,12 +26850,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26898,12 +26898,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26946,12 +26946,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 36,769/36,769 (100%)</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 35,298/36,769 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -27042,12 +27042,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27090,12 +27090,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27138,12 +27138,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27186,12 +27186,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27234,12 +27234,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27282,12 +27282,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27330,12 +27330,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 875,473/4,716,088 (18.6%)</t>
         </is>
       </c>
     </row>
@@ -27378,12 +27378,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27426,12 +27426,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27474,12 +27474,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27522,12 +27522,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 3,654,640/4,716,088 (77.5%)</t>
         </is>
       </c>
     </row>
@@ -27570,12 +27570,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -27618,12 +27618,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -27666,12 +27666,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -27714,12 +27714,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -27762,12 +27762,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -27810,12 +27810,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -27858,12 +27858,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -27906,12 +27906,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -27954,12 +27954,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,885/5,885 (100%)</t>
         </is>
       </c>
     </row>
@@ -28002,12 +28002,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,885/5,885 (100%)</t>
         </is>
       </c>
     </row>
@@ -28050,12 +28050,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+          <t>비영 5,884/5,885 (100.0%)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정(동명통과)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정(동명통과)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정(동명통과)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11062,7 +11062,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -11076,12 +11080,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>비영 1,260/1,260 (100%)</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11110,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -11120,12 +11128,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>비영 1,260/1,260 (100%)</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11158,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -11164,12 +11176,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>비영 1,260/1,260 (100%)</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11206,11 @@
           <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -11208,12 +11224,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>비영 1,260/1,260 (100%)</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11254,11 @@
           <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -11257,7 +11277,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>전건 NULL (0/1,260)</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11302,11 @@
           <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -11301,7 +11325,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>전건 NULL (0/1,260)</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11350,11 @@
           <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
@@ -11345,7 +11373,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>`FACT_TARGET_PROJECT` 0행 — 원천 미입고</t>
+          <t>전건 NULL (0/1,260)</t>
         </is>
       </c>
     </row>
@@ -11778,6 +11806,390 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>비영 36,769/36,769 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GOAL_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.GOAL_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.GOAL_TYPE_NM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>비영 1,260/1,260 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CPR_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.CPR_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.CPR_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>비영 1,260/1,260 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ORG_PATH</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DIM_ORG.ORG_PATH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRM_ORG.USE_YN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>비영 1,305/1,315 (99.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SRC_TEAM_NM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.SRC_TEAM_NM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.ORG_NM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>비영 1,260/1,260 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SRC_SPONSOR_BIZ_NM</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.SRC_SPONSOR_BIZ_NM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.SPONSOR_BIZ_NM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>비영 1,260/1,260 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NEW_OLD_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.NEW_OLD_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.NEW_OLD_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>비영 820/1,260 (65.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ORG_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.ORG_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.ORG_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>비영 1,260/1,260 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WIDE_TARGET_BIZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DTL_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FACT_TARGET_PROJECT.DTL_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.DTL_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>비영 338/1,260 (26.8%)</t>
         </is>
       </c>
     </row>
@@ -13510,12 +13922,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 48,457/77,505 (62.5%)</t>
+          <t>비영 77,505/77,505 (100%)</t>
         </is>
       </c>
     </row>
@@ -17052,12 +17464,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -17249,7 +17661,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 2/2 (100%)</t>
+          <t>비영 4/4 (100%)</t>
         </is>
       </c>
     </row>
@@ -18050,12 +18462,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -18727,7 +19139,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 2/2 (100%)</t>
+          <t>비영 4/4 (100%)</t>
         </is>
       </c>
     </row>
@@ -18775,7 +19187,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 2/2 (100%)</t>
+          <t>비영 4/4 (100%)</t>
         </is>
       </c>
     </row>
@@ -18896,12 +19308,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -18944,12 +19356,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -18992,12 +19404,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -19040,12 +19452,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 98,168/1,663,437 (5.9%)</t>
         </is>
       </c>
     </row>
@@ -19088,12 +19500,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -19136,12 +19548,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 452,903/1,663,437 (27.2%)</t>
         </is>
       </c>
     </row>
@@ -19184,12 +19596,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -19232,12 +19644,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,545,982/1,663,437 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -19280,12 +19692,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 330,438/1,663,437 (19.9%)</t>
         </is>
       </c>
     </row>
@@ -19328,12 +19740,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 995,447/1,663,437 (59.8%)</t>
         </is>
       </c>
     </row>
@@ -19376,12 +19788,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,663,437/1,663,437 (100%)</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19841,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>전건 NULL (0/1,663,437)</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19889,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>전건 NULL (0/1,663,437)</t>
         </is>
       </c>
     </row>
@@ -19520,12 +19932,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,545,982/1,663,437 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -19568,12 +19980,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>`FACT_BIGQUERY_BEHAVIOR` 0행 — 원천 미입고</t>
+          <t>비영 1,529,725/1,663,437 (92.0%)</t>
         </is>
       </c>
     </row>
@@ -19808,12 +20220,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20412,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,785,300)</t>
+          <t>비영 39,773/1,785,300 (2.2%)</t>
         </is>
       </c>
     </row>
@@ -20048,12 +20460,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1/1 (100%)</t>
+          <t>비영 47,858/47,859 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20096,12 +20508,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1/1 (100%)</t>
+          <t>비영 47,842/47,859 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20144,12 +20556,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1/1 (100%)</t>
+          <t>비영 47,856/47,859 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20192,12 +20604,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1/1 (100%)</t>
+          <t>비영 469/480 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -20240,12 +20652,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1/1 (100%)</t>
+          <t>비영 467/480 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -20288,12 +20700,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1)</t>
+          <t>비영 479/480 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -20336,12 +20748,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1)</t>
+          <t>비영 479/480 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -20384,12 +20796,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1)</t>
+          <t>비영 479/480 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -20437,7 +20849,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 2/2 (100%)</t>
+          <t>비영 4/4 (100%)</t>
         </is>
       </c>
     </row>
@@ -23276,12 +23688,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -26034,12 +26446,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/73,415) — 설계O·값 미주입</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 48,457/48,457 (100%)</t>
+          <t>비영 50,096/50,096 (100%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 58,678/77,505 (75.7%)</t>
+          <t>비영 245,204/271,175 (90.4%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 21,459/77,505 (27.7%)</t>
+          <t>비영 22,599/271,175 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 37,106/48,457 (76.6%)</t>
+          <t>비영 38,745/50,096 (77.3%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 32,718/48,457 (67.5%)</t>
+          <t>비영 34,316/50,096 (68.5%)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,104/48,457 (4.3%)</t>
+          <t>비영 2,104/50,096 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 33,721/48,457 (69.6%)</t>
+          <t>비영 35,319/50,096 (70.5%)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 15,993/48,457 (33.0%)</t>
+          <t>비영 17,591/50,096 (35.1%)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 45,121/48,457 (93.1%)</t>
+          <t>비영 46,760/50,096 (93.3%)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 36,009/48,457 (74.3%)</t>
+          <t>비영 37,607/50,096 (75.1%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 48,457/48,457 (100%)</t>
+          <t>비영 50,096/50,096 (100%)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 42,618/48,457 (88.0%)</t>
+          <t>비영 44,586/50,096 (89.0%)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 14,990/48,457 (30.9%)</t>
+          <t>비영 16,588/50,096 (33.1%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,933/48,457 (68.0%)</t>
+          <t>비영 35,539/50,096 (70.9%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 35,002/48,457 (72.2%)</t>
+          <t>비영 36,641/50,096 (73.1%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 32,902/48,457 (67.9%)</t>
+          <t>비영 34,500/50,096 (68.9%)</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 45,974/48,457 (94.9%)</t>
+          <t>비영 47,992/50,096 (95.8%)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 2,104/48,457 (4.3%)</t>
+          <t>비영 2,104/50,096 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 35,943/48,457 (74.2%)</t>
+          <t>비영 37,541/50,096 (74.9%)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/48,457)</t>
+          <t>전건 NULL (0/50,096)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 7,953/48,457 (16.4%)</t>
+          <t>비영 7,953/50,096 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 7,953/48,457 (16.4%)</t>
+          <t>비영 7,953/50,096 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 13,971/48,457 (28.8%)</t>
+          <t>비영 14,795/50,096 (29.5%)</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 17,801/48,457 (36.7%)</t>
+          <t>비영 18,832/50,096 (37.6%)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 3,366/3,367 (100.0%)</t>
+          <t>비영 9,679/9,696 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 3,357/3,367 (99.7%)</t>
+          <t>비영 9,686/9,696 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 52,657/41,935,344 (0.1%)</t>
+          <t>비영 50,401/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8629,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 52,407/41,935,344 (0.1%)</t>
+          <t>비영 50,173/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8677,12 +8677,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 34,332/41,935,344 (0.1%)</t>
+          <t>비영 34,059/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 34,106/41,935,344 (0.1%)</t>
+          <t>비영 33,882/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 30,696/41,935,344 (0.1%)</t>
+          <t>비영 26,873/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 30,187/41,935,344 (0.1%)</t>
+          <t>비영 26,416/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8869,12 +8869,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 157,097/41,935,344 (0.4%)</t>
+          <t>비영 111,268/41,935,344 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -8917,12 +8917,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 70,027/41,935,344 (0.2%)</t>
+          <t>비영 34,342/41,935,344 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -8965,12 +8965,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.TIT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+          <t>CRM_SEND_REQUEST.SEND_STATUS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,260)</t>
+          <t>전건 NULL (0/2,966)</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,260)</t>
+          <t>전건 NULL (0/2,966)</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,260)</t>
+          <t>전건 NULL (0/2,966)</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,966/2,966 (100%)</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 1,260/2,966 (42.5%)</t>
         </is>
       </c>
     </row>
@@ -12040,12 +12040,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 2,786/2,966 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 820/1,260 (65.1%)</t>
+          <t>비영 2,526/2,966 (85.2%)</t>
         </is>
       </c>
     </row>
@@ -12136,12 +12136,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,260/1,260 (100%)</t>
+          <t>비영 1,804/2,966 (60.8%)</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 338/1,260 (26.8%)</t>
+          <t>비영 440/2,966 (14.8%)</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,104/48,457 (4.3%)</t>
+          <t>비영 2,104/50,096 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 36,009/48,457 (74.3%)</t>
+          <t>비영 37,607/50,096 (75.1%)</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 48,457/48,457 (100%)</t>
+          <t>비영 50,096/50,096 (100%)</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 45,121/48,457 (93.1%)</t>
+          <t>비영 46,760/50,096 (93.3%)</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -13735,7 +13735,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/77,505) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/271,175) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 19,952/77,505 (25.7%)</t>
+          <t>비영 151,450/271,175 (55.8%)</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/77,505) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/271,175) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 58,678/77,505 (75.7%)</t>
+          <t>비영 245,204/271,175 (90.4%)</t>
         </is>
       </c>
     </row>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 23,255/77,505 (30.0%)</t>
+          <t>비영 210,773/271,175 (77.7%)</t>
         </is>
       </c>
     </row>
@@ -14071,7 +14071,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 25,148/77,505 (32.4%)</t>
+          <t>비영 189,300/271,175 (69.8%)</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 21,459/77,505 (27.7%)</t>
+          <t>비영 22,599/271,175 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,949/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,948/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -14407,7 +14407,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,025/29,048 (3.5%)</t>
+          <t>비영 1,033/221,079 (0.5%)</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 2,904/29,048 (10.0%)</t>
+          <t>비영 2,927/221,079 (1.3%)</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -14546,12 +14546,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 29,048/29,048 (100%)</t>
+          <t>비영 105,384/221,079 (47.7%)</t>
         </is>
       </c>
     </row>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 29,048/29,048 (100%)</t>
+          <t>비영 221,079/221,079 (100%)</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 6,392/29,048 (22.0%)</t>
+          <t>비영 6,392/221,079 (2.9%)</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 15,893/29,048 (54.7%)</t>
+          <t>비영 17,738/221,079 (8.0%)</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 4,226/29,048 (14.5%)</t>
+          <t>비영 4,767/221,079 (2.2%)</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 18,563/29,048 (63.9%)</t>
+          <t>비영 178,990/221,079 (81.0%)</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 20,064/29,048 (69.1%)</t>
+          <t>비영 201,795/221,079 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 6,226/29,048 (21.4%)</t>
+          <t>비영 49,087/221,079 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 6,226/29,048 (21.4%)</t>
+          <t>비영 49,085/221,079 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 6,392/29,048 (22.0%)</t>
+          <t>비영 6,392/221,079 (2.9%)</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 37,106/48,457 (76.6%)</t>
+          <t>비영 38,745/50,096 (77.3%)</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 32,718/48,457 (67.5%)</t>
+          <t>비영 34,316/50,096 (68.5%)</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,104/48,457 (4.3%)</t>
+          <t>비영 2,104/50,096 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 33,721/48,457 (69.6%)</t>
+          <t>비영 35,319/50,096 (70.5%)</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 15,993/48,457 (33.0%)</t>
+          <t>비영 17,591/50,096 (35.1%)</t>
         </is>
       </c>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 45,121/48,457 (93.1%)</t>
+          <t>비영 46,760/50,096 (93.3%)</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,009/48,457 (74.3%)</t>
+          <t>비영 37,607/50,096 (75.1%)</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 48,457/48,457 (100%)</t>
+          <t>비영 50,096/50,096 (100%)</t>
         </is>
       </c>
     </row>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 42,618/48,457 (88.0%)</t>
+          <t>비영 44,586/50,096 (89.0%)</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 14,990/48,457 (30.9%)</t>
+          <t>비영 16,588/50,096 (33.1%)</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,933/48,457 (68.0%)</t>
+          <t>비영 35,539/50,096 (70.9%)</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 35,002/48,457 (72.2%)</t>
+          <t>비영 36,641/50,096 (73.1%)</t>
         </is>
       </c>
     </row>
@@ -15703,7 +15703,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 32,902/48,457 (67.9%)</t>
+          <t>비영 34,500/50,096 (68.9%)</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 45,974/48,457 (94.9%)</t>
+          <t>비영 47,992/50,096 (95.8%)</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 2,104/48,457 (4.3%)</t>
+          <t>비영 2,104/50,096 (4.2%)</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 35,943/48,457 (74.2%)</t>
+          <t>비영 37,541/50,096 (74.9%)</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/48,457)</t>
+          <t>전건 NULL (0/50,096)</t>
         </is>
       </c>
     </row>
@@ -15943,7 +15943,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 7,953/48,457 (16.4%)</t>
+          <t>비영 7,953/50,096 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 7,953/48,457 (16.4%)</t>
+          <t>비영 7,953/50,096 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 13,971/48,457 (28.8%)</t>
+          <t>비영 14,795/50,096 (29.5%)</t>
         </is>
       </c>
     </row>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 17,801/48,457 (36.7%)</t>
+          <t>비영 18,832/50,096 (37.6%)</t>
         </is>
       </c>
     </row>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 29,048/29,048 (100%)</t>
+          <t>비영 221,079/221,079 (100%)</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -16309,7 +16309,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 58,678/77,505 (75.7%)</t>
+          <t>비영 245,204/271,175 (90.4%)</t>
         </is>
       </c>
     </row>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 23,255/77,505 (30.0%)</t>
+          <t>비영 210,773/271,175 (77.7%)</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 25,148/77,505 (32.4%)</t>
+          <t>비영 189,300/271,175 (69.8%)</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,949/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,948/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,025/29,048 (3.5%)</t>
+          <t>비영 1,033/221,079 (0.5%)</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 2,904/29,048 (10.0%)</t>
+          <t>비영 2,927/221,079 (1.3%)</t>
         </is>
       </c>
     </row>
@@ -16693,7 +16693,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -16736,12 +16736,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 29,048/29,048 (100%)</t>
+          <t>비영 105,384/221,079 (47.7%)</t>
         </is>
       </c>
     </row>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 29,048/29,048 (100%)</t>
+          <t>비영 221,079/221,079 (100%)</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 6,392/29,048 (22.0%)</t>
+          <t>비영 6,392/221,079 (2.9%)</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 NULL (0/29,048)</t>
+          <t>전건 NULL (0/221,079)</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 15,893/29,048 (54.7%)</t>
+          <t>비영 17,738/221,079 (8.0%)</t>
         </is>
       </c>
     </row>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 4,226/29,048 (14.5%)</t>
+          <t>비영 4,767/221,079 (2.2%)</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 18,563/29,048 (63.9%)</t>
+          <t>비영 178,990/221,079 (81.0%)</t>
         </is>
       </c>
     </row>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 20,064/29,048 (69.1%)</t>
+          <t>비영 201,795/221,079 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17173,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 6,226/29,048 (21.4%)</t>
+          <t>비영 49,087/221,079 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 6,226/29,048 (21.4%)</t>
+          <t>비영 49,085/221,079 (22.2%)</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 6,392/29,048 (22.0%)</t>
+          <t>비영 6,392/221,079 (2.9%)</t>
         </is>
       </c>
     </row>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 3,366/3,367 (100.0%)</t>
+          <t>비영 9,679/9,696 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 3,357/3,367 (99.7%)</t>
+          <t>비영 9,686/9,696 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 58,678/77,505 (75.7%)</t>
+          <t>비영 245,204/271,175 (90.4%)</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 23,255/77,505 (30.0%)</t>
+          <t>비영 210,773/271,175 (77.7%)</t>
         </is>
       </c>
     </row>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 25,148/77,505 (32.4%)</t>
+          <t>비영 189,300/271,175 (69.8%)</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 21,459/77,505 (27.7%)</t>
+          <t>비영 22,599/271,175 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,949/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 7,139/77,505 (9.2%)</t>
+          <t>비영 50,948/271,175 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -18219,7 +18219,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 77,505/77,505 (100%)</t>
+          <t>비영 271,175/271,175 (100%)</t>
         </is>
       </c>
     </row>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 3,367/3,367 (100%)</t>
+          <t>비영 9,696/9,696 (100%)</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 3,366/3,367 (100.0%)</t>
+          <t>비영 9,679/9,696 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 3,366/3,367 (100.0%)</t>
+          <t>비영 9,695/9,696 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,367)</t>
+          <t>전건 NULL (0/9,696)</t>
         </is>
       </c>
     </row>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 3,357/3,367 (99.7%)</t>
+          <t>비영 9,686/9,696 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 3,366/3,367 (100.0%)</t>
+          <t>비영 6,423/9,696 (66.2%)</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,367)</t>
+          <t>전건 NULL (0/9,696)</t>
         </is>
       </c>
     </row>
@@ -19313,7 +19313,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 98,168/1,663,437 (5.9%)</t>
+          <t>비영 80,624/1,398,512 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 452,903/1,663,437 (27.2%)</t>
+          <t>비영 374,079/1,398,512 (26.7%)</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,545,982/1,663,437 (92.9%)</t>
+          <t>비영 1,302,628/1,398,512 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 330,438/1,663,437 (19.9%)</t>
+          <t>비영 294,660/1,398,512 (21.1%)</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 995,447/1,663,437 (59.8%)</t>
+          <t>비영 1,003,028/1,398,512 (71.7%)</t>
         </is>
       </c>
     </row>
@@ -19793,7 +19793,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 1,663,437/1,663,437 (100%)</t>
+          <t>비영 1,398,512/1,398,512 (100%)</t>
         </is>
       </c>
     </row>
@@ -19841,7 +19841,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,663,437)</t>
+          <t>전건 NULL (0/1,398,512)</t>
         </is>
       </c>
     </row>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,663,437)</t>
+          <t>전건 NULL (0/1,398,512)</t>
         </is>
       </c>
     </row>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 1,545,982/1,663,437 (92.9%)</t>
+          <t>비영 1,302,628/1,398,512 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -19985,7 +19985,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 1,529,725/1,663,437 (92.0%)</t>
+          <t>비영 1,282,053/1,398,512 (91.7%)</t>
         </is>
       </c>
     </row>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 39,773/1,785,300 (2.2%)</t>
+          <t>비영 30,397/1,785,300 (1.7%)</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 47,858/47,859 (100.0%)</t>
+          <t>비영 41,761/41,762 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20513,7 +20513,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 47,842/47,859 (100.0%)</t>
+          <t>비영 41,745/41,762 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20561,7 +20561,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 47,856/47,859 (100.0%)</t>
+          <t>비영 41,759/41,762 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 469/480 (97.7%)</t>
+          <t>비영 521/533 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 467/480 (97.3%)</t>
+          <t>비영 518/533 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 479/480 (99.8%)</t>
+          <t>비영 532/533 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 479/480 (99.8%)</t>
+          <t>비영 532/533 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -20801,7 +20801,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 479/480 (99.8%)</t>
+          <t>비영 532/533 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -22803,7 +22803,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PRZWIN_CD</t>
+          <t>CRM_EVENT_PARTICIPATION.SELF_PARTCPT_CD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -22824,12 +22824,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,248,727)</t>
+          <t>비영 162,441/1,248,727 (13.0%)</t>
         </is>
       </c>
     </row>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -13751,7 +13751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15253,6 +15253,354 @@
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MATCH_BASIS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RECEIVED_SADAN_FLAG</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RECEIVED_SADAN_FLAG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RECEIVED_SABOK_FLAG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RECEIVED_SABOK_FLAG</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RECEIVED_TONGHAP_FLAG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RECEIVED_TONGHAP_FLAG</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CHRG_DEPT_NAMES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CHRG_DEPT_NAMES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SVC_CATEGORY_NAMES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SVC_CATEGORY_NAMES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CULTURE_EVENT_PART_ROWS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ONLINE_EVENT_PART_ROWS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ONLINE_EVENT_PART_ROWS_AFTER</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ONLINE_EVENT_PART_ROWS_AFTER</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>

--- a/30_output_share/04_컬럼계보매핑.xlsx
+++ b/30_output_share/04_컬럼계보매핑.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 50,103/50,103 (100%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 252,475/279,202 (90.4%)</t>
+          <t>비영 249,697/274,105 (91.1%)</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 22,607/279,202 (8.1%)</t>
+          <t>비영 22,726/274,105 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 38,752/50,103 (77.3%)</t>
+          <t>비영 39,006/49,863 (78.2%)</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 34,316/50,103 (68.5%)</t>
+          <t>비영 34,413/49,863 (69.0%)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,111/50,103 (4.2%)</t>
+          <t>비영 2,190/49,863 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 35,319/50,103 (70.5%)</t>
+          <t>비영 35,442/49,863 (71.1%)</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 17,591/50,103 (35.1%)</t>
+          <t>비영 17,714/49,863 (35.5%)</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 46,767/50,103 (93.3%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 37,614/50,103 (75.1%)</t>
+          <t>비영 37,810/49,863 (75.8%)</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 50,103/50,103 (100%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 44,586/50,103 (89.0%)</t>
+          <t>비영 22,890/49,863 (45.9%)</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 16,588/50,103 (33.1%)</t>
+          <t>비영 16,685/49,863 (33.5%)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 35,539/50,103 (70.9%)</t>
+          <t>비영 35,657/49,863 (71.5%)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,641/50,103 (73.1%)</t>
+          <t>비영 36,817/49,863 (73.8%)</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 34,500/50,103 (68.9%)</t>
+          <t>비영 34,597/49,863 (69.4%)</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 47,992/50,103 (95.8%)</t>
+          <t>비영 47,673/49,863 (95.6%)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 2,111/50,103 (4.2%)</t>
+          <t>비영 2,190/49,863 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 37,548/50,103 (74.9%)</t>
+          <t>비영 37,742/49,863 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/50,103)</t>
+          <t>전건 NULL (0/49,863)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 7,961/50,103 (15.9%)</t>
+          <t>비영 7,937/49,863 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 7,961/50,103 (15.9%)</t>
+          <t>비영 7,937/49,863 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 14,795/50,103 (29.5%)</t>
+          <t>비영 14,838/49,863 (29.8%)</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 18,832/50,103 (37.6%)</t>
+          <t>비영 18,815/49,863 (37.7%)</t>
         </is>
       </c>
     </row>
@@ -1774,8 +1774,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -1784,7 +1792,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1814,8 +1822,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -1824,7 +1840,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1854,8 +1870,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -1864,7 +1888,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1894,8 +1918,16 @@
           <t>DIM_DATE.QUARTER</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -1904,7 +1936,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1934,8 +1966,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -1944,7 +1984,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2002,7 +2042,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2090,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 9,829/9,846 (99.8%)</t>
+          <t>비영 9,639/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2138,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 9,836/9,846 (99.9%)</t>
+          <t>비영 9,642/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2299,7 +2339,11 @@
           <t>DATA_TYPE_NM</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DATA_TYPE_NM</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -2332,21 +2376,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IS_FORECAST</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>DATA_TYPE_STD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MAP_EXT_DATA_TYPE.DATA_TYPE_STD</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>미해석</t>
+          <t>직접참조</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>미해석</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2368,21 +2416,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SPNSR_BSNS_GRP_NM</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>IS_FORECAST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MAP_EXT_DATA_TYPE.IS_FORECAST</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>미해석</t>
+          <t>직접참조</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>미해석</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2404,7 +2456,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NEW_EXST_DIV_NM</t>
+          <t>SPNSR_BSNS_GRP_NM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -2440,7 +2492,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HDQ_BRNCH_GRP_NM</t>
+          <t>NEW_EXST_DIV_NM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -2476,7 +2528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DVLP_CNT</t>
+          <t>HDQ_BRNCH_GRP_NM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -2512,7 +2564,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CMLT_DVLP_CNT</t>
+          <t>DVLP_CNT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -2548,7 +2600,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADJ_DSCNTC_RT</t>
+          <t>CMLT_DVLP_CNT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -2584,7 +2636,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADJ_DSCNTC_CNT</t>
+          <t>ADJ_DSCNTC_RT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -2620,7 +2672,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ADJ_RDCAMT_RT</t>
+          <t>ADJ_DSCNTC_CNT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -2656,7 +2708,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADJ_RDCAMT_CNT</t>
+          <t>ADJ_RDCAMT_RT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -2692,7 +2744,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADJ_RECALC_DSCNTC_RT</t>
+          <t>ADJ_RDCAMT_CNT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -2728,7 +2780,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADJ_DSCNTC_CNT2</t>
+          <t>ADJ_RECALC_DSCNTC_RT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2764,7 +2816,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADJ_CMLT_DSCNTC_CNT</t>
+          <t>ADJ_DSCNTC_CNT2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -2800,7 +2852,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DSCNTC_RT</t>
+          <t>ADJ_CMLT_DSCNTC_CNT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -2836,7 +2888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DSCNTC_CNT</t>
+          <t>DSCNTC_RT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -2872,7 +2924,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RDCAMT_RT</t>
+          <t>DSCNTC_CNT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -2908,7 +2960,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SPNSR_BSNS_CHN_DEC_CNT</t>
+          <t>RDCAMT_RT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -2944,7 +2996,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RDCAMT_CNT</t>
+          <t>SPNSR_BSNS_CHN_DEC_CNT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -2980,7 +3032,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CMLT_EOM_ACT_MBER_CNT</t>
+          <t>RDCAMT_CNT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -3016,7 +3068,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CMLT_ACT_MBER_CNT</t>
+          <t>CMLT_EOM_ACT_MBER_CNT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -3052,7 +3104,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ACT_RT</t>
+          <t>CMLT_ACT_MBER_CNT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -3088,7 +3140,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADJ_MT_PAY_RT</t>
+          <t>ACT_RT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -3124,7 +3176,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADJ_MBRFEE_AMT</t>
+          <t>ADJ_MT_PAY_RT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -3160,7 +3212,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADJ_CMLT_PAY_RT</t>
+          <t>ADJ_MBRFEE_AMT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -3196,7 +3248,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADJ_CMLT_MBRFEE_AMT</t>
+          <t>ADJ_CMLT_PAY_RT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -3232,7 +3284,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CMLT_PAY_RT</t>
+          <t>ADJ_CMLT_MBRFEE_AMT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -3268,7 +3320,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CMLT_MBRFEE_AMT</t>
+          <t>CMLT_PAY_RT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -3304,7 +3356,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MBRFEE_DIFF_AMT</t>
+          <t>CMLT_MBRFEE_AMT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -3327,6 +3379,42 @@
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WIDE_MBRFEE_PRDT_ACTL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MBRFEE_DIFF_AMT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
@@ -3343,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3454,7 +3542,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 4,756,975/4,757,065 (100.0%)</t>
+          <t>비영 4,778,836/4,778,926 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3590,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 4,757,065/4,757,065 (100%)</t>
+          <t>비영 4,778,926/4,778,926 (100%)</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3638,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 4,757,065/4,757,065 (100%)</t>
+          <t>비영 4,778,926/4,778,926 (100%)</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3686,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 3,684,236/4,757,065 (77.4%)</t>
+          <t>비영 3,701,086/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3734,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 3,684,236/4,757,065 (77.4%)</t>
+          <t>비영 3,701,086/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3782,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 3,684,185/4,757,065 (77.4%)</t>
+          <t>비영 3,701,035/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3830,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 1,982,027/4,757,065 (41.7%)</t>
+          <t>비영 1,990,875/4,778,926 (41.7%)</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3878,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,982,027/4,757,065 (41.7%)</t>
+          <t>비영 1,990,875/4,778,926 (41.7%)</t>
         </is>
       </c>
     </row>
@@ -3802,17 +3890,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STOP_CNT</t>
+          <t>DEV_CNT_RAW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.DEV_CNT_RAW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3838,7 +3926,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 2,352,632/4,778,926 (49.2%)</t>
         </is>
       </c>
     </row>
@@ -3850,17 +3938,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STOP_MEMBERS</t>
+          <t>DEV_EXCL_REASON</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.DEV_EXCL_REASON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_MEMBER_DEV.SPNSR_AMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3886,7 +3974,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 392,959/4,778,926 (8.2%)</t>
         </is>
       </c>
     </row>
@@ -3898,22 +3986,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNPAID_STOP_CNT</t>
+          <t>STOP_CNT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.UNPAID_STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CNT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3924,7 +4012,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3934,7 +4022,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 394,363/4,757,065 (8.3%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -3946,22 +4034,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNPAID_STOP_MEMBERS</t>
+          <t>STOP_MEMBERS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.UNPAID_STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3972,7 +4060,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3982,7 +4070,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 394,363/4,757,065 (8.3%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -3994,22 +4082,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JOIN_DATE</t>
+          <t>UNPAID_STOP_CNT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.JOIN_DATE</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_CNT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -4030,7 +4118,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 3,684,236/4,757,065 (77.4%)</t>
+          <t>비영 394,363/4,778,926 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -4042,17 +4130,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STOP_DATE</t>
+          <t>UNPAID_STOP_MEMBERS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_DATE</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_MEMBERS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.SPNSR_DSCNTC_DE</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_NM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4078,7 +4166,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 394,363/4,778,926 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -4090,22 +4178,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STOP_REASON</t>
+          <t>JOIN_DATE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_REASON</t>
+          <t>FACT_MEMBER_EVENT.JOIN_DATE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_CD</t>
+          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4126,7 +4214,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 3,701,086/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -4138,17 +4226,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL</t>
+          <t>STOP_DATE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_CHANNEL</t>
+          <t>FACT_MEMBER_EVENT.STOP_DATE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH</t>
+          <t>CRM_MEMBER_DISCONTINUE.SPNSR_DSCNTC_DE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4174,7 +4262,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4274,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STOP_REASON_NM</t>
+          <t>STOP_REASON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_REASON_NM</t>
+          <t>FACT_MEMBER_EVENT.STOP_REASON</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_NM</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_CD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4222,7 +4310,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -4234,17 +4322,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP_CHANNEL_NM</t>
+          <t>STOP_CHANNEL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.STOP_CHANNEL_NM</t>
+          <t>FACT_MEMBER_EVENT.STOP_CHANNEL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH_NM</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4270,7 +4358,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -4282,22 +4370,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NEW_EXISTING_FLAG</t>
+          <t>STOP_REASON_NM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.NEW_EXISTING_FLAG</t>
+          <t>FACT_MEMBER_EVENT.STOP_REASON_NM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_RSN_NM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4313,12 +4401,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 4,757,065/4,757,065 (100%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -4330,22 +4418,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AGE_AT_EVENT</t>
+          <t>STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.AGE_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.STOP_CHANNEL_NM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_MEMBER_DISCONTINUE.DSCNTC_PATH_NM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_SPNSR_DSCNTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4366,7 +4454,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 3,684,236/4,757,065 (77.4%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -4378,22 +4466,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AGE_BAND_AT_EVENT</t>
+          <t>NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.AGE_BAND_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.NEW_EXISTING_FLAG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.OCCRRNC_DE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4409,12 +4497,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 3,684,236/4,757,065 (77.4%)</t>
+          <t>비영 4,778,926/4,778,926 (100%)</t>
         </is>
       </c>
     </row>
@@ -4426,17 +4514,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AREA_CD_AT_EVENT</t>
+          <t>AGE_AT_EVENT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.AREA_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.AGE_AT_EVENT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4462,7 +4550,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,684,230/4,757,065 (77.4%)</t>
+          <t>비영 3,701,086/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -4474,22 +4562,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REGION_AT_EVENT</t>
+          <t>AGE_BAND_AT_EVENT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.REGION_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.AGE_BAND_AT_EVENT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_NM</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -4510,7 +4598,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 3,663,533/4,757,065 (77.0%)</t>
+          <t>비영 3,701,086/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -4522,16 +4610,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>AREA_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>FACT_MEMBER_EVENT.AREA_CD_AT_EVENT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
@@ -4540,17 +4636,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 73,415/73,415 (100%)</t>
+          <t>비영 3,701,078/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -4562,16 +4658,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>REGION_AT_EVENT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>FACT_MEMBER_EVENT.REGION_AT_EVENT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.AREA_NM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
@@ -4580,7 +4684,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4590,7 +4694,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 73,414/73,415 (100.0%)</t>
+          <t>비영 3,680,376/4,778,926 (77.0%)</t>
         </is>
       </c>
     </row>
@@ -4602,16 +4706,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -4620,17 +4732,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 73,414/73,415 (100.0%)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -4642,16 +4754,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>DIM_DATE.YEAR</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -4660,17 +4780,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 73,415/73,415 (100%)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4682,16 +4802,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>DIM_DATE.MONTH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -4700,7 +4828,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4722,16 +4850,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>QUARTER</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_DATE.QUARTER</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -4740,17 +4876,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 73,414/73,415 (100.0%)</t>
+          <t>비영 73,415/73,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -4762,16 +4898,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -4780,7 +4924,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4790,7 +4934,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 251/73,415 (0.3%)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4802,22 +4946,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>QUARTER</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.SEX</t>
+          <t>DIM_DATE.QUARTER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX</t>
+          <t>CRM_HOLIDAY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TM_CM_SCHDUL_MNG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -4828,7 +4972,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4838,7 +4982,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 73,414/73,415 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4850,22 +4994,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.SEX_NM</t>
+          <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX_NM</t>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TM_CM_SCHDUL_MNG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -4886,7 +5030,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 251/73,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -4898,22 +5042,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.GENDER_NAME</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.SEX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -4934,7 +5078,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4946,22 +5090,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.AREA_CD</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.SEX_NM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -4982,7 +5126,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 7,951,939/8,141,302 (97.7%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -4994,12 +5138,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.REGION</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.GENDER_NAME</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5030,7 +5174,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,894,232/8,141,302 (97.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5042,17 +5186,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.AGE</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.AREA_CD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5078,7 +5222,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,993/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5234,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.AGE_BAND</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.REGION</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5126,7 +5270,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,916,257/8,163,553 (97.0%)</t>
         </is>
       </c>
     </row>
@@ -5138,22 +5282,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.MBER_STAT_CD</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.AGE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -5174,7 +5318,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,963,585/8,141,302 (97.8%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5330,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.AGE_BAND</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -5222,7 +5366,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 8,141,301/8,141,302 (100.0%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5378,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PREV_MBER_STAT_CD</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.PREV_MBER_STAT_CD</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5270,7 +5414,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,639,405/8,141,302 (93.8%)</t>
+          <t>비영 7,985,631/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -5282,22 +5426,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PREV_MEMBER_STATUS_NAME</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.PREV_MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -5318,7 +5462,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,639,405/8,141,302 (93.8%)</t>
+          <t>비영 8,163,552/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5330,17 +5474,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.MBER_DIV_CD</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.PREV_MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5361,12 +5505,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 7,656,533/8,163,553 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5522,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>PREV_MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.PREV_MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5409,12 +5553,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 7,656,533/8,163,553 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5570,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JOIN_PATH_CD</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.JOIN_PATH_CD</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.JOIN_PATH_CD</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5457,12 +5601,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,963,582/8,141,302 (97.8%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -5474,22 +5618,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MEMBER_ENROLL_PATH_NAME</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_STATUS_HISTORY.ENROLL_PATH_NAME</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -5505,12 +5649,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 8,141,298/8,141,302 (100.0%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -5522,22 +5666,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>JOIN_PATH_CD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.JOIN_PATH_CD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_MEMBER.JOIN_PATH_CD</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -5553,12 +5697,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 7,985,628/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -5570,22 +5714,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>MEMBER_ENROLL_PATH_NAME</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_MEMBER_STATUS_HISTORY.ENROLL_PATH_NAME</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5606,7 +5750,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 8,163,549/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5618,17 +5762,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAMPAIGN_PARENT</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.UPPER_CMPGN_CD</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5649,12 +5793,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -5666,17 +5810,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5697,12 +5841,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5714,17 +5858,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAMPAIGN_PROMO_METHOD</t>
+          <t>CAMPAIGN_PARENT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.PROMO_METHOD</t>
+          <t>DIM_CAMPAIGN.PARENT_CAMPAIGN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.PR_MTH_CD</t>
+          <t>CRM_CAMPAIGN.UPPER_CMPGN_CD</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5750,7 +5894,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5762,17 +5906,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAMPAIGN_CATEGORY</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CMPGN_CTGR_NM_AT_EVENT</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5793,12 +5937,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -5810,17 +5954,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAMPAIGN_INFLOW_PATH</t>
+          <t>CAMPAIGN_PROMO_METHOD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.MBER_INFLOW_PATH_NM_AT_EVENT</t>
+          <t>DIM_CAMPAIGN.PROMO_METHOD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.MBER_INFLOW_PATH_NM</t>
+          <t>CRM_CAMPAIGN.PR_MTH_CD</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5846,7 +5990,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -5858,17 +6002,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAMPAIGN_DOMESTIC_OVERSEAS</t>
+          <t>CAMPAIGN_CATEGORY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CMPGN_TYPE1_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_CTGR_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_TYPE1_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5894,7 +6038,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -5906,17 +6050,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BIZ_CASE_TYPE</t>
+          <t>CAMPAIGN_INFLOW_PATH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CMPGN_TYPE2_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_TYPE2_NM</t>
+          <t>CRM_CAMPAIGN.MBER_INFLOW_PATH_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5942,7 +6086,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -5954,17 +6098,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAMPAIGN_MARKETING_CAMPAIGN</t>
+          <t>CAMPAIGN_DOMESTIC_OVERSEAS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.MKTG_CMPGN_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE1_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.MK_CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE1_NM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5990,7 +6134,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6146,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CAMPAIGN_CMMN_BRND</t>
+          <t>CAMPAIGN_BIZ_CASE_TYPE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CMMN_BRND_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE2_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMMN_BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE2_NM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6038,7 +6182,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 3,683,281/4,757,065 (77.4%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6050,17 +6194,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMPAIGN_MKTG_UTM</t>
+          <t>CAMPAIGN_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.MKTG_UTM_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.MKTG_UTM_NM</t>
+          <t>CRM_CAMPAIGN.MK_CMPGN_NM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6086,7 +6230,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 886,137/4,757,065 (18.6%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6098,17 +6242,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAMPAIGN_SPNSR_DIV_CD</t>
+          <t>CAMPAIGN_CMMN_BRND</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.SPNSR_DIV_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.CMMN_BRND_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.SPNSR_DIV_CD</t>
+          <t>CRM_CAMPAIGN.CMMN_BRND_NM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6134,7 +6278,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 3,684,218/4,757,065 (77.4%)</t>
+          <t>비영 3,700,335/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6146,17 +6290,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMPAIGN_SPNSR_DIV_NM</t>
+          <t>CAMPAIGN_MKTG_UTM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.SPNSR_DIV_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.SPNSR_DIV_NM</t>
+          <t>CRM_CAMPAIGN.MKTG_UTM_NM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6182,7 +6326,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 3,684,218/4,757,065 (77.4%)</t>
+          <t>비영 890,219/4,778,926 (18.6%)</t>
         </is>
       </c>
     </row>
@@ -6194,17 +6338,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CAMPAIGN_CPR_DIV_CD</t>
+          <t>CAMPAIGN_SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CPR_DIV_CD_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CPR_DIV_CD</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6230,7 +6374,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 3,684,218/4,757,065 (77.4%)</t>
+          <t>비영 3,701,068/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6242,17 +6386,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CAMPAIGN_CPR_DIV_NM</t>
+          <t>CAMPAIGN_SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_EVENT.CPR_DIV_NM_AT_EVENT</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CPR_DIV_NM</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6278,7 +6422,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 3,684,218/4,757,065 (77.4%)</t>
+          <t>비영 3,701,068/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6290,22 +6434,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_CPR_DIV_CD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_CD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -6321,12 +6465,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,701,068/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6338,22 +6482,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>CAMPAIGN_CPR_DIV_NM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_NM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -6369,12 +6513,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,701,068/4,778,926 (77.4%)</t>
         </is>
       </c>
     </row>
@@ -6386,22 +6530,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_DIV_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -6417,12 +6561,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -6434,22 +6578,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_GROUP_NAME</t>
+          <t>SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -6465,12 +6609,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 50/51 (98.0%)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -6482,22 +6626,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_CPR_DIV_CD</t>
+          <t>SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.CPR_DIV_CD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.CPR_DIV_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -6530,12 +6674,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_CPR_DIV_NM</t>
+          <t>SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.CPR_DIV_NM</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6578,22 +6722,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>SPONSORSHIP_CPR_DIV_CD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>DIM_SPONSORSHIP.CPR_DIV_CD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_SPONSORSHIP.CPR_DIV_CD</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -6609,12 +6753,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -6626,22 +6770,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>SPONSORSHIP_CPR_DIV_NM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>DIM_SPONSORSHIP.CPR_DIV_NM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -6657,12 +6801,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -6674,17 +6818,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>ORG_CORP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>DIM_ORG.CORP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6705,12 +6849,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -6722,17 +6866,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>ORG_DIVISION</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>DIM_ORG.DIVISION</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6770,22 +6914,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>ORG_DEPARTMENT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_CODE</t>
+          <t>DIM_ORG.DEPARTMENT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -6806,7 +6950,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -6818,22 +6962,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>REASON_NAME</t>
+          <t>ORG_TEAM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_NAME</t>
+          <t>DIM_ORG.TEAM</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -6849,12 +6993,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -6866,17 +7010,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>REASON_TYPE</t>
+          <t>REASON_CODE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_TYPE</t>
+          <t>DIM_REASON.REASON_CODE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CRM_CODE.CD_ID</t>
+          <t>CRM_CODE.DTL_CD_ID</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6897,12 +7041,108 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>비영 5,884/5,885 (100.0%)</t>
+          <t>비영 5,917/5,917 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>REASON_NAME</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_NAME</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>비영 5,917/5,917 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CRM_CODE.CD_ID</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>비영 5,916/5,917 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7268,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 42,624,063/42,624,113 (100.0%)</t>
+          <t>비영 43,386,518/43,386,568 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7316,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 42,624,063/42,624,113 (100.0%)</t>
+          <t>비영 43,386,518/43,386,568 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7364,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 42,624,063/42,624,113 (100.0%)</t>
+          <t>비영 43,386,518/43,386,568 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7412,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 42,624,113/42,624,113 (100%)</t>
+          <t>비영 43,386,568/43,386,568 (100%)</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7460,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 42,546,049/42,624,113 (99.8%)</t>
+          <t>비영 43,307,574/43,386,568 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7652,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 41,974,264/42,624,113 (98.5%)</t>
+          <t>비영 42,736,313/43,386,568 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7700,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 41,974,264/42,624,113 (98.5%)</t>
+          <t>비영 42,736,313/43,386,568 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7748,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 42,624,113/42,624,113 (100%)</t>
+          <t>비영 43,386,568/43,386,568 (100%)</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7796,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 42,424,317/42,624,113 (99.5%)</t>
+          <t>비영 43,185,522/43,386,568 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7892,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 42,604,693/42,624,113 (100.0%)</t>
+          <t>비영 43,367,148/43,386,568 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7940,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 40,636,646/42,624,113 (95.3%)</t>
+          <t>비영 40,691,261/43,386,568 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -7720,8 +7960,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -7730,7 +7978,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7788,7 +8036,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 41,974,263/42,624,113 (98.5%)</t>
+          <t>비영 42,736,312/43,386,568 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -7836,7 +8084,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,619,081/1,796,798 (90.1%)</t>
+          <t>비영 1,625,973/1,803,895 (90.1%)</t>
         </is>
       </c>
     </row>
@@ -7884,7 +8132,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,796,797/1,796,798 (100.0%)</t>
+          <t>비영 1,803,894/1,803,895 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7932,7 +8180,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,796,798/1,796,798 (100%)</t>
+          <t>비영 1,803,895/1,803,895 (100%)</t>
         </is>
       </c>
     </row>
@@ -7980,7 +8228,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,796,798/1,796,798 (100%)</t>
+          <t>비영 1,803,895/1,803,895 (100%)</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8276,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,796,253/1,796,798 (100.0%)</t>
+          <t>비영 1,803,339/1,803,895 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8324,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,796,253/1,796,798 (100.0%)</t>
+          <t>비영 1,803,339/1,803,895 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8364,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8404,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8444,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8484,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8524,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8564,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8604,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,617,659/1,617,660 (100.0%)</t>
+          <t>비영 1,624,547/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8644,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8684,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8724,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8764,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8804,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 1,606,247/1,617,660 (99.3%)</t>
+          <t>비영 1,613,134/1,624,548 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8844,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8884,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8924,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8964,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8756,7 +9004,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8796,7 +9044,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 383,572/1,617,660 (23.7%)</t>
+          <t>비영 384,367/1,624,548 (23.7%)</t>
         </is>
       </c>
     </row>
@@ -8836,7 +9084,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8876,7 +9124,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -8924,7 +9172,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 41,974,085/42,624,113 (98.5%)</t>
+          <t>비영 42,736,133/43,386,568 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -8972,7 +9220,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 40,626,963/42,624,113 (95.3%)</t>
+          <t>비영 40,681,515/43,386,568 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9268,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 39,979,951/42,624,113 (93.8%)</t>
+          <t>비영 40,034,097/43,386,568 (92.3%)</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9316,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,701,244/42,624,113 (8.7%)</t>
+          <t>비영 4,410,637/43,386,568 (10.2%)</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9364,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 42,624,113/42,624,113 (100%)</t>
+          <t>비영 43,386,568/43,386,568 (100%)</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9412,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 3,701,248/42,624,113 (8.7%)</t>
+          <t>비영 4,410,642/43,386,568 (10.2%)</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9538,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 42,272,088/42,272,226 (100.0%)</t>
+          <t>비영 42,981,519/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9586,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 42,272,088/42,272,226 (100.0%)</t>
+          <t>비영 42,981,519/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9634,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 42,272,088/42,272,226 (100.0%)</t>
+          <t>비영 42,981,519/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9682,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 42,272,226/42,272,226 (100%)</t>
+          <t>비영 42,981,657/42,981,657 (100%)</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9730,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 1,879,345/42,272,226 (4.4%)</t>
+          <t>비영 1,887,796/42,981,657 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9778,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 1,879,345/42,272,226 (4.4%)</t>
+          <t>비영 1,887,796/42,981,657 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -9552,12 +9800,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -9568,7 +9816,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9578,7 +9826,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 1,002,567/42,272,226 (2.4%)</t>
+          <t>비영 1,007,090/42,981,657 (2.3%)</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9874,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 3,454,270/42,272,226 (8.2%)</t>
+          <t>비영 4,110,632/42,981,657 (9.6%)</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9922,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9970,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 40,606,430/42,272,226 (96.1%)</t>
+          <t>비영 41,310,673/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -9770,7 +10018,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 41,096,945/42,272,226 (97.2%)</t>
+          <t>비영 41,805,091/42,981,657 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -9818,7 +10066,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 41,096,953/42,272,226 (97.2%)</t>
+          <t>비영 41,805,099/42,981,657 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -9866,7 +10114,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 1,853,923/42,272,226 (4.4%)</t>
+          <t>비영 1,862,172/42,981,657 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -9914,7 +10162,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 1,853,923/42,272,226 (4.4%)</t>
+          <t>비영 1,862,172/42,981,657 (4.3%)</t>
         </is>
       </c>
     </row>
@@ -9962,7 +10210,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 116,591/42,272,226 (0.3%)</t>
+          <t>비영 117,537/42,981,657 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10258,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,238,774/42,272,226 (2.9%)</t>
+          <t>비영 1,244,416/42,981,657 (2.9%)</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10306,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 37,524,187/42,272,226 (88.8%)</t>
+          <t>비영 38,154,459/42,981,657 (88.8%)</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10354,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 38,365,691/42,272,226 (90.8%)</t>
+          <t>비영 39,040,306/42,981,657 (90.8%)</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10402,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10450,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 39,872,779/42,272,226 (94.3%)</t>
+          <t>비영 40,573,727/42,981,657 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10498,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/42,272,226) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/42,981,657) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10546,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,499,776/42,272,226 (8.3%)</t>
+          <t>비영 4,158,818/42,981,657 (9.7%)</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10594,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 37,509,013/42,272,226 (88.7%)</t>
+          <t>비영 37,557,563/42,981,657 (87.4%)</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10642,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 29,606/42,272,226 (0.1%)</t>
+          <t>비영 29,855/42,981,657 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10690,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 643,823/42,272,226 (1.5%)</t>
+          <t>비영 644,219/42,981,657 (1.5%)</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10738,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 38,169,183/42,272,226 (90.3%)</t>
+          <t>비영 38,218,610/42,981,657 (88.9%)</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10786,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 39,331,147/42,272,226 (93.0%)</t>
+          <t>비영 40,037,011/42,981,657 (93.1%)</t>
         </is>
       </c>
     </row>
@@ -10586,7 +10834,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/42,272,226) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/42,981,657) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10882,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/42,272,226) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/42,981,657) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10930,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 2,038,889/42,272,226 (4.8%)</t>
+          <t>비영 2,048,077/42,981,657 (4.8%)</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10978,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 4,565,414/42,272,226 (10.8%)</t>
+          <t>비영 4,644,746/42,981,657 (10.8%)</t>
         </is>
       </c>
     </row>
@@ -10778,7 +11026,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 308,911/42,272,226 (0.7%)</t>
+          <t>비영 310,290/42,981,657 (0.7%)</t>
         </is>
       </c>
     </row>
@@ -10826,7 +11074,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 115,833/42,272,226 (0.3%)</t>
+          <t>비영 116,758/42,981,657 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -10874,7 +11122,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 42,272,084/42,272,226 (100.0%)</t>
+          <t>비영 42,981,515/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -10922,7 +11170,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 3,074,942/42,272,226 (7.3%)</t>
+          <t>비영 3,121,762/42,981,657 (7.3%)</t>
         </is>
       </c>
     </row>
@@ -10970,7 +11218,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11266,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11314,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 42,272,084/42,272,226 (100.0%)</t>
+          <t>비영 42,981,515/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11362,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 42,272,084/42,272,226 (100.0%)</t>
+          <t>비영 42,981,515/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11410,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 40,482,455/42,272,226 (95.8%)</t>
+          <t>비영 41,184,797/42,981,657 (95.8%)</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11458,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 34,876,662/42,272,226 (82.5%)</t>
+          <t>비영 35,493,090/42,981,657 (82.6%)</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11506,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 39,374,597/42,272,226 (93.1%)</t>
+          <t>비영 40,071,883/42,981,657 (93.2%)</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11554,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 42,272,084/42,272,226 (100.0%)</t>
+          <t>비영 42,981,515/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11602,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 3,389,985/42,272,226 (8.0%)</t>
+          <t>비영 3,447,710/42,981,657 (8.0%)</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11650,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 3,499,776/42,272,226 (8.3%)</t>
+          <t>비영 4,158,818/42,981,657 (9.7%)</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11698,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11746,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11794,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11842,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 7,951,939/8,141,302 (97.7%)</t>
+          <t>비영 7,973,993/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11890,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 7,894,232/8,141,302 (97.0%)</t>
+          <t>비영 7,916,257/8,163,553 (97.0%)</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11938,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11986,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -11786,7 +12034,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 7,963,585/8,141,302 (97.8%)</t>
+          <t>비영 7,985,631/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -11834,7 +12082,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 8,141,301/8,141,302 (100.0%)</t>
+          <t>비영 8,163,552/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11882,7 +12130,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 7,639,405/8,141,302 (93.8%)</t>
+          <t>비영 7,656,533/8,163,553 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -11930,7 +12178,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 7,639,405/8,141,302 (93.8%)</t>
+          <t>비영 7,656,533/8,163,553 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12226,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12274,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12322,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 8,141,301/8,141,302 (100.0%)</t>
+          <t>비영 8,163,552/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12370,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 7,962,192/8,141,302 (97.8%)</t>
+          <t>비영 7,984,238/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12418,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 7,963,582/8,141,302 (97.8%)</t>
+          <t>비영 7,985,628/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12466,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>비영 8,141,298/8,141,302 (100.0%)</t>
+          <t>비영 8,163,549/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12514,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>비영 7,962,062/8,141,302 (97.8%)</t>
+          <t>비영 7,984,104/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12562,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>비영 1,616,438/8,141,302 (19.9%)</t>
+          <t>비영 1,623,033/8,163,553 (19.9%)</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12610,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12658,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12706,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12754,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12802,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -12602,7 +12850,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 35,294/37,164 (95.0%)</t>
+          <t>비영 35,719/37,346 (95.6%)</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13282,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>비영 5,917/5,917 (100%)</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13330,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>비영 5,885/5,885 (100%)</t>
+          <t>비영 5,917/5,917 (100%)</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13378,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>비영 5,884/5,885 (100.0%)</t>
+          <t>비영 5,916/5,917 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13504,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 42,272,088/42,272,226 (100.0%)</t>
+          <t>비영 42,981,519/42,981,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13588,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 4,757,065/4,757,065 (100%)</t>
+          <t>비영 4,778,926/4,778,926 (100%)</t>
         </is>
       </c>
     </row>
@@ -13388,7 +13636,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 1,982,027/4,757,065 (41.7%)</t>
+          <t>비영 1,990,875/4,778,926 (41.7%)</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13684,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13732,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13780,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 37,524,187/42,272,226 (88.8%)</t>
+          <t>비영 38,154,459/42,981,657 (88.8%)</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13828,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 39,872,779/42,272,226 (94.3%)</t>
+          <t>비영 40,573,727/42,981,657 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13850,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -13618,7 +13866,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -13628,7 +13876,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,072,829/4,757,065 (22.6%)</t>
+          <t>비영 1,077,840/4,778,926 (22.6%)</t>
         </is>
       </c>
     </row>
@@ -13751,7 +13999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13847,7 +14095,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CTE경유·다중후보(DIM_MEMBER_ACQUISITION,FACT_EVENT_ATTENDANCE,FACT_MEMBER_EVENT,FACT_MESSAGE_DISPATCH)</t>
+          <t>CTE경유·다중후보(DIM_MEMBER_ACQUISITION,FACT_EVENT_ATTENDANCE,FACT_MEMBER_EVENT,FACT_MEMBER_FEE,FACT_MEMBER_MONTHLY,FACT_MEMBER_SPONSORSHIP_SPAN,FACT_MESSAGE_DISPATCH)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -13862,7 +14110,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -14402,8 +14650,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
@@ -14412,7 +14668,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -14442,8 +14698,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -14452,7 +14716,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -14482,8 +14746,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
@@ -14492,7 +14764,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -14542,7 +14814,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,617,640/1,617,660 (100.0%)</t>
+          <t>비영 1,624,528/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14854,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14894,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14662,7 +14934,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14974,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14742,7 +15014,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,616,970/1,617,660 (100.0%)</t>
+          <t>비영 1,624,001/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14782,7 +15054,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14822,7 +15094,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,617,656/1,617,660 (100.0%)</t>
+          <t>비영 1,624,544/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -14862,7 +15134,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -14902,7 +15174,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,617,660/1,617,660 (100%)</t>
+          <t>비영 1,624,548/1,624,548 (100%)</t>
         </is>
       </c>
     </row>
@@ -14942,7 +15214,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,606,247/1,617,660 (99.3%)</t>
+          <t>비영 1,613,134/1,624,548 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -14982,7 +15254,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,617,657/1,617,660 (100.0%)</t>
+          <t>비영 1,624,545/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15294,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,617,633/1,617,660 (100.0%)</t>
+          <t>비영 1,624,521/1,624,548 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15334,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 916,244/1,617,660 (56.6%)</t>
+          <t>비영 920,296/1,624,548 (56.6%)</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15374,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 928,986/1,617,660 (57.4%)</t>
+          <t>비영 933,149/1,624,548 (57.4%)</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15414,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 928,986/1,617,660 (57.4%)</t>
+          <t>비영 933,149/1,624,548 (57.4%)</t>
         </is>
       </c>
     </row>
@@ -15601,6 +15873,246 @@
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RETAINED_3M_FLAG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RETAINED_3M_FLAG</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RETAINED_6M_FLAG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RETAINED_6M_FLAG</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RETAINED_12M_FLAG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RETAINED_12M_FLAG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_SERVICE_COHORT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PAID_AFTER_3M_FLAG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PAID_AFTER_3M_FLAG</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>미해석</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>census 대상 아님(뷰 파생·차원 라벨 등)</t>
         </is>
@@ -15728,7 +16240,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 43,440,831/43,440,831 (100%)</t>
+          <t>비영 44,626,415/44,626,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -15776,7 +16288,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 43,440,831/43,440,831 (100%)</t>
+          <t>비영 44,626,415/44,626,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -15824,7 +16336,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 43,440,831/43,440,831 (100%)</t>
+          <t>비영 44,626,415/44,626,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -15872,7 +16384,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 25,826,805/43,440,831 (59.5%)</t>
+          <t>비영 26,127,308/44,626,415 (58.5%)</t>
         </is>
       </c>
     </row>
@@ -15920,7 +16432,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 2,055,449/43,440,831 (4.7%)</t>
+          <t>비영 2,070,335/44,626,415 (4.6%)</t>
         </is>
       </c>
     </row>
@@ -15968,7 +16480,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 524,428/43,440,831 (1.2%)</t>
+          <t>비영 552,187/44,626,415 (1.2%)</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16528,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/43,440,831) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/44,626,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16576,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/43,440,831) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/44,626,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16624,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/43,440,831) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/44,626,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16672,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/43,440,831) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/44,626,415) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -16208,7 +16720,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 51,931/43,440,831 (0.1%)</t>
+          <t>비영 55,973/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16768,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 51,700/43,440,831 (0.1%)</t>
+          <t>비영 55,714/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16816,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 37,842/43,440,831 (0.1%)</t>
+          <t>비영 38,092/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16864,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 37,648/43,440,831 (0.1%)</t>
+          <t>비영 37,875/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16400,7 +16912,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 27,958/43,440,831 (0.1%)</t>
+          <t>비영 32,301/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16960,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 27,485/43,440,831 (0.1%)</t>
+          <t>비영 31,765/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16496,7 +17008,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 113,912/43,440,831 (0.3%)</t>
+          <t>비영 122,297/44,626,415 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -16544,7 +17056,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 35,217/43,440,831 (0.1%)</t>
+          <t>비영 36,275/44,626,415 (0.1%)</t>
         </is>
       </c>
     </row>
@@ -16566,7 +17078,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.TIT</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_TOP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -16592,7 +17104,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 746,102/43,440,831 (1.7%)</t>
+          <t>비영 746,103/44,626,415 (1.7%)</t>
         </is>
       </c>
     </row>
@@ -16614,12 +17126,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
+          <t>CRM_SEND_REQUEST.SEND_GBN_TOP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -16630,7 +17142,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -16640,7 +17152,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 734,692/43,440,831 (1.7%)</t>
+          <t>비영 734,696/44,626,415 (1.6%)</t>
         </is>
       </c>
     </row>
@@ -16688,7 +17200,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 41,372,108/43,440,831 (95.2%)</t>
+          <t>비영 42,545,990/44,626,415 (95.3%)</t>
         </is>
       </c>
     </row>
@@ -16736,7 +17248,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 40,476,298/43,440,831 (93.2%)</t>
+          <t>비영 41,647,423/44,626,415 (93.3%)</t>
         </is>
       </c>
     </row>
@@ -16784,7 +17296,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 43,440,831/43,440,831 (100%)</t>
+          <t>비영 44,626,415/44,626,415 (100%)</t>
         </is>
       </c>
     </row>
@@ -16832,7 +17344,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 22,130,322/43,440,831 (50.9%)</t>
+          <t>비영 22,448,709/44,626,415 (50.3%)</t>
         </is>
       </c>
     </row>
@@ -16880,7 +17392,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 22,130,322/43,440,831 (50.9%)</t>
+          <t>비영 22,448,709/44,626,415 (50.3%)</t>
         </is>
       </c>
     </row>
@@ -16928,7 +17440,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 30,713,604/43,440,831 (70.7%)</t>
+          <t>비영 31,863,317/44,626,415 (71.4%)</t>
         </is>
       </c>
     </row>
@@ -16976,7 +17488,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 28,998,604/43,440,831 (66.8%)</t>
+          <t>비영 30,088,870/44,626,415 (67.4%)</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17536,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 28,998,604/43,440,831 (66.8%)</t>
+          <t>비영 30,088,870/44,626,415 (67.4%)</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17584,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/43,440,831)</t>
+          <t>전건 NULL (0/44,626,415)</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17632,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 NULL (0/43,440,831)</t>
+          <t>전건 NULL (0/44,626,415)</t>
         </is>
       </c>
     </row>
@@ -17140,8 +17652,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -17150,7 +17670,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -17180,8 +17700,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -17190,7 +17718,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -17220,8 +17748,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -17230,7 +17766,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -17260,8 +17796,16 @@
           <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -17270,7 +17814,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -17300,8 +17844,16 @@
           <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -17310,7 +17862,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -17340,8 +17892,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
@@ -17350,7 +17910,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -17408,7 +17968,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17456,7 +18016,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17504,7 +18064,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17552,7 +18112,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,951,939/8,141,302 (97.7%)</t>
+          <t>비영 7,973,993/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -17600,7 +18160,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,894,232/8,141,302 (97.0%)</t>
+          <t>비영 7,916,257/8,163,553 (97.0%)</t>
         </is>
       </c>
     </row>
@@ -17648,7 +18208,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -17696,7 +18256,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -17744,7 +18304,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,963,585/8,141,302 (97.8%)</t>
+          <t>비영 7,985,631/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -17792,7 +18352,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 8,141,301/8,141,302 (100.0%)</t>
+          <t>비영 8,163,552/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17840,7 +18400,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -17888,7 +18448,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -17936,7 +18496,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 73/74 (98.6%)</t>
+          <t>비영 74/75 (98.7%)</t>
         </is>
       </c>
     </row>
@@ -17984,7 +18544,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 74/74 (100%)</t>
+          <t>비영 75/75 (100%)</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18592,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 73/74 (98.6%)</t>
+          <t>비영 74/75 (98.7%)</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18640,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 74/74 (100%)</t>
+          <t>비영 75/75 (100%)</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18688,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 73/74 (98.6%)</t>
+          <t>비영 74/75 (98.7%)</t>
         </is>
       </c>
     </row>
@@ -18176,7 +18736,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 74/74 (100%)</t>
+          <t>비영 75/75 (100%)</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18880,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -18368,7 +18928,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18976,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18464,7 +19024,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -18512,7 +19072,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19386,7 +19946,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19434,7 +19994,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -19482,7 +20042,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -19530,7 +20090,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -19700,7 +20260,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -19748,7 +20308,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19796,7 +20356,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -19914,7 +20474,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_ORG.USE_YN</t>
+          <t>CRM_ORG_CLEAN.ORG_PATH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -20520,7 +21080,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -20568,7 +21128,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -20616,7 +21176,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20664,7 +21224,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -20912,7 +21472,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -20960,7 +21520,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21760,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,111/50,103 (4.2%)</t>
+          <t>비영 2,190/49,863 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21808,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 37,614/50,103 (75.1%)</t>
+          <t>비영 37,810/49,863 (75.8%)</t>
         </is>
       </c>
     </row>
@@ -21296,7 +21856,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 50,103/50,103 (100%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -21339,12 +21899,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 46,767/50,103 (93.3%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -21364,8 +21924,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
@@ -21374,7 +21942,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -21404,8 +21972,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -21414,7 +21990,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -21444,8 +22020,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
@@ -21454,7 +22038,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -21484,8 +22068,16 @@
           <t>DIM_DATE.QUARTER</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -21494,7 +22086,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -21552,7 +22144,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -21567,7 +22159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21678,7 +22270,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -21726,7 +22318,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -21774,7 +22366,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/279,202) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/274,105) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21796,12 +22388,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCY_AD_PERFORMANCE.AD_SOURCE_TYPE</t>
+          <t>CRM_CAMPAIGN.MKTG_UTM_NM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -21822,7 +22414,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 156,898/279,202 (56.2%)</t>
+          <t>비영 241,699/274,105 (88.2%)</t>
         </is>
       </c>
     </row>
@@ -21870,7 +22462,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/279,202) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/274,105) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21918,7 +22510,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -21966,7 +22558,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 252,475/279,202 (90.4%)</t>
+          <t>비영 249,697/274,105 (91.1%)</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22606,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 218,127/279,202 (78.1%)</t>
+          <t>비영 215,149/274,105 (78.5%)</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 195,942/279,202 (70.2%)</t>
+          <t>비영 191,983/274,105 (70.0%)</t>
         </is>
       </c>
     </row>
@@ -22110,7 +22702,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 22,607/279,202 (8.1%)</t>
+          <t>비영 22,726/274,105 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -22158,7 +22750,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 52,336/279,202 (18.7%)</t>
+          <t>비영 50,621/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -22206,7 +22798,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 52,335/279,202 (18.7%)</t>
+          <t>비영 50,620/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -22254,7 +22846,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22894,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -22350,7 +22942,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22990,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,109/229,099 (0.5%)</t>
+          <t>비영 744/224,242 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -22446,7 +23038,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 4,420/229,099 (1.9%)</t>
+          <t>비영 3,433/224,242 (1.5%)</t>
         </is>
       </c>
     </row>
@@ -22494,7 +23086,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -22542,7 +23134,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 113,404/229,099 (49.5%)</t>
+          <t>비영 108,541/224,242 (48.4%)</t>
         </is>
       </c>
     </row>
@@ -22590,7 +23182,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 229,099/229,099 (100%)</t>
+          <t>비영 224,242/224,242 (100%)</t>
         </is>
       </c>
     </row>
@@ -22638,7 +23230,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 9,525/229,099 (4.2%)</t>
+          <t>비영 9,991/224,242 (4.5%)</t>
         </is>
       </c>
     </row>
@@ -22686,7 +23278,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -22734,7 +23326,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -22782,7 +23374,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 23,653/229,099 (10.3%)</t>
+          <t>비영 21,009/224,242 (9.4%)</t>
         </is>
       </c>
     </row>
@@ -22830,7 +23422,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 5,636/229,099 (2.5%)</t>
+          <t>비영 4,373/224,242 (2.0%)</t>
         </is>
       </c>
     </row>
@@ -22878,7 +23470,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 185,524/229,099 (81.0%)</t>
+          <t>비영 182,692/224,242 (81.5%)</t>
         </is>
       </c>
     </row>
@@ -22926,7 +23518,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 209,066/229,099 (91.3%)</t>
+          <t>비영 206,189/224,242 (91.9%)</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23566,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 50,450/229,099 (22.0%)</t>
+          <t>비영 49,038/224,242 (21.9%)</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23614,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 50,448/229,099 (22.0%)</t>
+          <t>비영 49,036/224,242 (21.9%)</t>
         </is>
       </c>
     </row>
@@ -23070,7 +23662,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 9,525/229,099 (4.2%)</t>
+          <t>비영 9,991/224,242 (4.5%)</t>
         </is>
       </c>
     </row>
@@ -23118,7 +23710,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 38,752/50,103 (77.3%)</t>
+          <t>비영 39,006/49,863 (78.2%)</t>
         </is>
       </c>
     </row>
@@ -23166,7 +23758,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 34,316/50,103 (68.5%)</t>
+          <t>비영 34,413/49,863 (69.0%)</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23806,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,111/50,103 (4.2%)</t>
+          <t>비영 2,190/49,863 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -23262,7 +23854,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 35,319/50,103 (70.5%)</t>
+          <t>비영 35,442/49,863 (71.1%)</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23902,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 17,591/50,103 (35.1%)</t>
+          <t>비영 17,714/49,863 (35.5%)</t>
         </is>
       </c>
     </row>
@@ -23353,12 +23945,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 46,767/50,103 (93.3%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -23406,7 +23998,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 37,614/50,103 (75.1%)</t>
+          <t>비영 37,810/49,863 (75.8%)</t>
         </is>
       </c>
     </row>
@@ -23454,7 +24046,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 50,103/50,103 (100%)</t>
+          <t>비영 49,863/49,863 (100%)</t>
         </is>
       </c>
     </row>
@@ -23502,7 +24094,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 44,586/50,103 (89.0%)</t>
+          <t>비영 22,890/49,863 (45.9%)</t>
         </is>
       </c>
     </row>
@@ -23550,7 +24142,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 16,588/50,103 (33.1%)</t>
+          <t>비영 16,685/49,863 (33.5%)</t>
         </is>
       </c>
     </row>
@@ -23598,7 +24190,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 35,539/50,103 (70.9%)</t>
+          <t>비영 35,657/49,863 (71.5%)</t>
         </is>
       </c>
     </row>
@@ -23646,7 +24238,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 36,641/50,103 (73.1%)</t>
+          <t>비영 36,817/49,863 (73.8%)</t>
         </is>
       </c>
     </row>
@@ -23694,7 +24286,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 34,500/50,103 (68.9%)</t>
+          <t>비영 34,597/49,863 (69.4%)</t>
         </is>
       </c>
     </row>
@@ -23742,7 +24334,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 47,992/50,103 (95.8%)</t>
+          <t>비영 47,673/49,863 (95.6%)</t>
         </is>
       </c>
     </row>
@@ -23790,7 +24382,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 2,111/50,103 (4.2%)</t>
+          <t>비영 2,190/49,863 (4.4%)</t>
         </is>
       </c>
     </row>
@@ -23838,7 +24430,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 37,548/50,103 (74.9%)</t>
+          <t>비영 37,742/49,863 (75.7%)</t>
         </is>
       </c>
     </row>
@@ -23886,7 +24478,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/50,103)</t>
+          <t>전건 NULL (0/49,863)</t>
         </is>
       </c>
     </row>
@@ -23934,7 +24526,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 7,961/50,103 (15.9%)</t>
+          <t>비영 7,937/49,863 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -23982,7 +24574,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 7,961/50,103 (15.9%)</t>
+          <t>비영 7,937/49,863 (15.9%)</t>
         </is>
       </c>
     </row>
@@ -24030,7 +24622,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 14,795/50,103 (29.5%)</t>
+          <t>비영 14,838/49,863 (29.8%)</t>
         </is>
       </c>
     </row>
@@ -24078,7 +24670,1111 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 18,832/50,103 (37.6%)</t>
+          <t>비영 18,815/49,863 (37.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MEDIA_CHANNEL_NM</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.MEDIA_CHANNEL_NM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.MEDIA_CHANNEL_NM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>비영 273,915/274,105 (99.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CREATIVE_NM</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CREATIVE_NM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.CREATIVE_NM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>비영 273,598/274,105 (99.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>COST_TYPE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.COST_TYPE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.COST_TYPE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>비영 274,105/274,105 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BDGT_SOURCE_NM</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.BDGT_SOURCE_NM</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.BDGT_SOURCE_NM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>비영 271,915/274,105 (99.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MATR_TY_NM</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.MATR_TY_NM</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.MATR_TY_NM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>비영 111,438/274,105 (40.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CMPGN_TYPE_BSN_NM</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CMPGN_TYPE_BSN_NM</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.CMPGN_TYPE_BSN_NM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>비영 224,242/274,105 (81.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UTM_CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.UTM_CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.UTM_CMPGN_NM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>비영 206,320/274,105 (75.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BSNS_CASE_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.BSNS_CASE_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_VIDEO.BSNS_CASE_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>비영 14,327/274,105 (5.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CM</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_VIDEO.BSNS_CASE_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>비영 35,620/274,105 (13.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DMST_OVSEA_DIV_NM</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.DMST_OVSEA_DIV_NM</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_VIDEO.DMST_OVSEA_DIV_NM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>비영 14,327/274,105 (5.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MKTG_MAP_METHOD</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.MKTG_MAP_METHOD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE;AGENCY_AD_ROW_DGT;AGENCY_AD_ROW_REBRDC;AGENCY_AD_ROW_VIDEO;CRM_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>테이블수준</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>비영 274,105/274,105 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AD_MAP_LEVEL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_MAP_LEVEL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE;AGENCY_AD_ROW_DGT;AGENCY_AD_ROW_REBRDC;AGENCY_AD_ROW_VIDEO;CRM_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>테이블수준</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>비영 46,988/274,105 (17.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AD_MAP_CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_MAP_CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>비영 39,254/274,105 (14.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AD_CTGR_CD</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CTGR_CD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_CD</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>비영 244,456/274,105 (89.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AD_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>비영 244,456/274,105 (89.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AD_CTGR_SRC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CTGR_SRC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>비영 274,105/274,105 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AD_CTGR_IS_MULTI</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CTGR_IS_MULTI</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>비영 161,343/274,105 (58.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AD_CTGR_NM_LIST</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.AD_CTGR_NM_LIST</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CRM_CAMPAIGN.CMPGN_CTGR_NM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>비영 244,456/274,105 (89.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UPPER_CAMPAIGN_CD</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.UPPER_CAMPAIGN_CD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.UPPER_CAMPAIGN_CD</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>비영 2,715/274,105 (1.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UPPER_CAMPAIGN_NM</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.UPPER_CAMPAIGN_NM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_PERFORMANCE.UPPER_CAMPAIGN_NM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS;REBRDC_AD_CMPGN_DTLS;VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>비영 4,086/274,105 (1.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CMPGN_TYPE1_BSN_NM</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CMPGN_TYPE1_BSN_NM</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.CMPGN_TYPE1_BSN_NM</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>비영 224,242/274,105 (81.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CMPGN_TYPE2_BSN_NM</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CMPGN_TYPE2_BSN_NM</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_DGT.CMPGN_TYPE2_BSN_NM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DGT_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>비영 224,242/274,105 (81.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WIDE_AD_COMBINED</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CMPGN_TY_NM</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FACT_AD_PERFORMANCE.CMPGN_TY_NM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AGENCY_AD_ROW_VIDEO.CMPGN_TY_NM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>VIDEO_AD_CMPGN_DTLS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>비영 14,327/274,105 (5.2%)</t>
         </is>
       </c>
     </row>
@@ -24204,7 +25900,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 229,099/229,099 (100%)</t>
+          <t>비영 224,242/224,242 (100%)</t>
         </is>
       </c>
     </row>
@@ -24252,7 +25948,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -24300,7 +25996,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -24348,7 +26044,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 252,475/279,202 (90.4%)</t>
+          <t>비영 249,697/274,105 (91.1%)</t>
         </is>
       </c>
     </row>
@@ -24396,7 +26092,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 218,127/279,202 (78.1%)</t>
+          <t>비영 215,149/274,105 (78.5%)</t>
         </is>
       </c>
     </row>
@@ -24444,7 +26140,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 195,942/279,202 (70.2%)</t>
+          <t>비영 191,983/274,105 (70.0%)</t>
         </is>
       </c>
     </row>
@@ -24492,7 +26188,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 52,336/279,202 (18.7%)</t>
+          <t>비영 50,621/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -24540,7 +26236,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 52,335/279,202 (18.7%)</t>
+          <t>비영 50,620/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -24588,7 +26284,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 1,109/229,099 (0.5%)</t>
+          <t>비영 744/224,242 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -24636,7 +26332,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 4,420/229,099 (1.9%)</t>
+          <t>비영 3,433/224,242 (1.5%)</t>
         </is>
       </c>
     </row>
@@ -24684,7 +26380,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -24732,7 +26428,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 113,404/229,099 (49.5%)</t>
+          <t>비영 108,541/224,242 (48.4%)</t>
         </is>
       </c>
     </row>
@@ -24780,7 +26476,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 229,099/229,099 (100%)</t>
+          <t>비영 224,242/224,242 (100%)</t>
         </is>
       </c>
     </row>
@@ -24828,7 +26524,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 9,525/229,099 (4.2%)</t>
+          <t>비영 9,991/224,242 (4.5%)</t>
         </is>
       </c>
     </row>
@@ -24876,7 +26572,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -24924,7 +26620,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 NULL (0/229,099)</t>
+          <t>전건 NULL (0/224,242)</t>
         </is>
       </c>
     </row>
@@ -24972,7 +26668,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 23,653/229,099 (10.3%)</t>
+          <t>비영 21,009/224,242 (9.4%)</t>
         </is>
       </c>
     </row>
@@ -25020,7 +26716,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 5,636/229,099 (2.5%)</t>
+          <t>비영 4,373/224,242 (2.0%)</t>
         </is>
       </c>
     </row>
@@ -25068,7 +26764,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 185,524/229,099 (81.0%)</t>
+          <t>비영 182,692/224,242 (81.5%)</t>
         </is>
       </c>
     </row>
@@ -25116,7 +26812,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 209,066/229,099 (91.3%)</t>
+          <t>비영 206,189/224,242 (91.9%)</t>
         </is>
       </c>
     </row>
@@ -25164,7 +26860,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 50,450/229,099 (22.0%)</t>
+          <t>비영 49,038/224,242 (21.9%)</t>
         </is>
       </c>
     </row>
@@ -25212,7 +26908,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 50,448/229,099 (22.0%)</t>
+          <t>비영 49,036/224,242 (21.9%)</t>
         </is>
       </c>
     </row>
@@ -25260,7 +26956,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 9,525/229,099 (4.2%)</t>
+          <t>비영 9,991/224,242 (4.5%)</t>
         </is>
       </c>
     </row>
@@ -25280,8 +26976,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
@@ -25290,7 +26994,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -25320,8 +27024,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
@@ -25330,7 +27042,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -25360,8 +27072,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -25370,7 +27090,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -25400,8 +27120,16 @@
           <t>DIM_DATE.QUARTER</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -25410,7 +27138,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -25440,8 +27168,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -25450,7 +27186,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -25508,7 +27244,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -25556,7 +27292,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 9,829/9,846 (99.8%)</t>
+          <t>비영 9,639/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -25604,7 +27340,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 9,836/9,846 (99.9%)</t>
+          <t>비영 9,642/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -25778,7 +27514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -25826,7 +27562,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -25874,7 +27610,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 252,475/279,202 (90.4%)</t>
+          <t>비영 249,697/274,105 (91.1%)</t>
         </is>
       </c>
     </row>
@@ -25922,7 +27658,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 218,127/279,202 (78.1%)</t>
+          <t>비영 215,149/274,105 (78.5%)</t>
         </is>
       </c>
     </row>
@@ -25970,7 +27706,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 195,942/279,202 (70.2%)</t>
+          <t>비영 191,983/274,105 (70.0%)</t>
         </is>
       </c>
     </row>
@@ -26018,7 +27754,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 22,607/279,202 (8.1%)</t>
+          <t>비영 22,726/274,105 (8.3%)</t>
         </is>
       </c>
     </row>
@@ -26066,7 +27802,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 52,336/279,202 (18.7%)</t>
+          <t>비영 50,621/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -26114,7 +27850,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 52,335/279,202 (18.7%)</t>
+          <t>비영 50,620/274,105 (18.5%)</t>
         </is>
       </c>
     </row>
@@ -26162,7 +27898,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -26210,7 +27946,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -26258,7 +27994,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 279,202/279,202 (100%)</t>
+          <t>비영 274,105/274,105 (100%)</t>
         </is>
       </c>
     </row>
@@ -26278,8 +28014,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -26288,7 +28032,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -26318,8 +28062,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
@@ -26328,7 +28080,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -26358,8 +28110,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -26368,7 +28128,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -26398,8 +28158,16 @@
           <t>DIM_DATE.QUARTER</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
@@ -26408,7 +28176,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -26438,8 +28206,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -26448,7 +28224,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -26506,7 +28282,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -26554,7 +28330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26602,7 +28378,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26650,7 +28426,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -26698,7 +28474,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26746,7 +28522,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 35,294/37,164 (95.0%)</t>
+          <t>비영 35,719/37,346 (95.6%)</t>
         </is>
       </c>
     </row>
@@ -26794,7 +28570,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 9,846/9,846 (100%)</t>
+          <t>비영 9,657/9,657 (100%)</t>
         </is>
       </c>
     </row>
@@ -26842,7 +28618,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 9,829/9,846 (99.8%)</t>
+          <t>비영 9,639/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -26890,7 +28666,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 9,845/9,846 (100.0%)</t>
+          <t>비영 9,656/9,657 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -26938,7 +28714,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,846)</t>
+          <t>전건 NULL (0/9,657)</t>
         </is>
       </c>
     </row>
@@ -26986,7 +28762,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 9,836/9,846 (99.9%)</t>
+          <t>비영 9,642/9,657 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -27034,7 +28810,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 6,573/9,846 (66.8%)</t>
+          <t>비영 5,154/9,657 (53.4%)</t>
         </is>
       </c>
     </row>
@@ -27082,7 +28858,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/9,846)</t>
+          <t>전건 NULL (0/9,657)</t>
         </is>
       </c>
     </row>
@@ -27193,7 +28969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27304,7 +29080,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27352,7 +29128,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27400,7 +29176,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27448,7 +29224,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 91,434/1,536,507 (6.0%)</t>
+          <t>비영 95,361/1,651,036 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -27496,7 +29272,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27544,7 +29320,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 429,007/1,536,507 (27.9%)</t>
+          <t>비영 443,226/1,651,036 (26.8%)</t>
         </is>
       </c>
     </row>
@@ -27592,7 +29368,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27640,7 +29416,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,428,691/1,536,507 (93.0%)</t>
+          <t>비영 1,533,545/1,651,036 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -27688,7 +29464,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 304,845/1,536,507 (19.8%)</t>
+          <t>비영 339,375/1,651,036 (20.6%)</t>
         </is>
       </c>
     </row>
@@ -27736,7 +29512,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 980,088/1,536,507 (63.8%)</t>
+          <t>비영 1,117,338/1,651,036 (67.7%)</t>
         </is>
       </c>
     </row>
@@ -27784,7 +29560,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 1,536,507/1,536,507 (100%)</t>
+          <t>비영 1,651,036/1,651,036 (100%)</t>
         </is>
       </c>
     </row>
@@ -27832,7 +29608,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,536,507)</t>
+          <t>전건 NULL (0/1,651,036)</t>
         </is>
       </c>
     </row>
@@ -27880,7 +29656,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,536,507)</t>
+          <t>전건 NULL (0/1,651,036)</t>
         </is>
       </c>
     </row>
@@ -27928,7 +29704,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 1,428,691/1,536,507 (93.0%)</t>
+          <t>비영 1,533,545/1,651,036 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -27976,7 +29752,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 1,411,320/1,536,507 (91.9%)</t>
+          <t>비영 1,515,785/1,651,036 (91.8%)</t>
         </is>
       </c>
     </row>
@@ -27996,8 +29772,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -28006,7 +29790,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -28036,8 +29820,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
@@ -28046,7 +29838,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -28076,8 +29868,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
@@ -28086,7 +29886,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -28116,8 +29916,16 @@
           <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
@@ -28126,7 +29934,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -28156,8 +29964,16 @@
           <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
@@ -28166,7 +29982,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -28196,8 +30012,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
@@ -28206,7 +30030,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -28264,7 +30088,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,796,799/1,796,799 (100%)</t>
+          <t>비영 1,803,896/1,803,896 (100%)</t>
         </is>
       </c>
     </row>
@@ -28312,7 +30136,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,796,799/1,796,799 (100%)</t>
+          <t>비영 1,803,896/1,803,896 (100%)</t>
         </is>
       </c>
     </row>
@@ -28360,7 +30184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,796,799)</t>
+          <t>전건 NULL (0/1,803,896)</t>
         </is>
       </c>
     </row>
@@ -28408,7 +30232,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 36,574/1,796,799 (2.0%)</t>
+          <t>비영 36,532/1,803,896 (2.0%)</t>
         </is>
       </c>
     </row>
@@ -28456,7 +30280,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 40,810/40,811 (100.0%)</t>
+          <t>비영 49,891/49,892 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -28504,7 +30328,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 40,794/40,811 (100.0%)</t>
+          <t>비영 49,876/49,892 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -28552,7 +30376,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 40,809/40,811 (100.0%)</t>
+          <t>비영 49,890/49,892 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -28600,7 +30424,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 471/481 (97.9%)</t>
+          <t>비영 473/482 (98.1%)</t>
         </is>
       </c>
     </row>
@@ -28648,7 +30472,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 467/481 (97.1%)</t>
+          <t>비영 469/482 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -28696,7 +30520,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 480/481 (99.8%)</t>
+          <t>비영 481/482 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -28744,7 +30568,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 480/481 (99.8%)</t>
+          <t>비영 481/482 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -28792,7 +30616,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 480/481 (99.8%)</t>
+          <t>비영 481/482 (99.8%)</t>
         </is>
       </c>
     </row>
@@ -28888,7 +30712,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -28936,7 +30760,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -28984,7 +30808,55 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WIDE_BIGQUERY_BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UTM_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FACT_BIGQUERY_BEHAVIOR.UTM_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BIGQUERY_EVENT.UTM_CAMPAIGN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>컬럼확정(동명통과)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>비영 803,509/1,651,036 (48.7%)</t>
         </is>
       </c>
     </row>
@@ -29110,7 +30982,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 1,488/1,488 (100%)</t>
+          <t>비영 2,436/2,436 (100%)</t>
         </is>
       </c>
     </row>
@@ -29158,7 +31030,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 1,488/1,488 (100%)</t>
+          <t>비영 2,436/2,436 (100%)</t>
         </is>
       </c>
     </row>
@@ -29206,7 +31078,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 1,488/1,488 (100%)</t>
+          <t>비영 2,436/2,436 (100%)</t>
         </is>
       </c>
     </row>
@@ -29254,7 +31126,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 297/1,488 (20.0%)</t>
+          <t>비영 788/2,436 (32.3%)</t>
         </is>
       </c>
     </row>
@@ -29302,7 +31174,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 400/1,488 (26.9%)</t>
+          <t>비영 1,032/2,436 (42.4%)</t>
         </is>
       </c>
     </row>
@@ -29350,7 +31222,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,488)</t>
+          <t>전건 NULL (0/2,436)</t>
         </is>
       </c>
     </row>
@@ -29398,7 +31270,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,488)</t>
+          <t>전건 NULL (0/2,436)</t>
         </is>
       </c>
     </row>
@@ -29446,7 +31318,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,488)</t>
+          <t>전건 NULL (0/2,436)</t>
         </is>
       </c>
     </row>
@@ -29468,7 +31340,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -29516,7 +31388,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -29564,7 +31436,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -29612,7 +31484,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_ORG_CLEAN.DEPT_NM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -29686,7 +31558,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 180/180 (100%)</t>
+          <t>비영 178/178 (100%)</t>
         </is>
       </c>
     </row>
@@ -29734,7 +31606,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 179/180 (99.4%)</t>
+          <t>비영 177/178 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -29782,7 +31654,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -29830,7 +31702,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -29878,7 +31750,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -30466,7 +32338,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -30514,7 +32386,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -30562,7 +32434,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -30584,7 +32456,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30610,7 +32482,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 109,804/994,533 (11.0%)</t>
+          <t>비영 111,959/1,008,268 (11.1%)</t>
         </is>
       </c>
     </row>
@@ -30632,7 +32504,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -30658,7 +32530,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 3,544/994,533 (0.4%)</t>
+          <t>비영 3,612/1,008,268 (0.4%)</t>
         </is>
       </c>
     </row>
@@ -30680,7 +32552,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -30706,7 +32578,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 53,583/994,533 (5.4%)</t>
+          <t>비영 55,224/1,008,268 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -30728,7 +32600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -30754,7 +32626,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -30776,7 +32648,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -30802,7 +32674,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 1,985/994,533 (0.2%)</t>
+          <t>비영 2,008/1,008,268 (0.2%)</t>
         </is>
       </c>
     </row>
@@ -30824,7 +32696,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_CD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -30850,7 +32722,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -30898,7 +32770,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 954,092/994,533 (95.9%)</t>
+          <t>비영 967,990/1,008,268 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -30946,7 +32818,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 133,809/994,533 (13.5%)</t>
+          <t>비영 136,639/1,008,268 (13.6%)</t>
         </is>
       </c>
     </row>
@@ -30994,7 +32866,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 17,596/994,533 (1.8%)</t>
+          <t>비영 18,262/1,008,268 (1.8%)</t>
         </is>
       </c>
     </row>
@@ -31042,7 +32914,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -31090,7 +32962,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 4,829/994,533 (0.5%)</t>
+          <t>비영 4,829/1,008,268 (0.5%)</t>
         </is>
       </c>
     </row>
@@ -31138,7 +33010,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 12,989/994,533 (1.3%)</t>
+          <t>비영 12,989/1,008,268 (1.3%)</t>
         </is>
       </c>
     </row>
@@ -31186,7 +33058,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 166,547/994,533 (16.7%)</t>
+          <t>비영 170,411/1,008,268 (16.9%)</t>
         </is>
       </c>
     </row>
@@ -31234,7 +33106,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 983,544/994,533 (98.9%)</t>
+          <t>비영 997,279/1,008,268 (98.9%)</t>
         </is>
       </c>
     </row>
@@ -31282,7 +33154,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 985,100/994,533 (99.1%)</t>
+          <t>비영 998,835/1,008,268 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -31330,7 +33202,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 827,497/994,533 (83.2%)</t>
+          <t>비영 837,368/1,008,268 (83.1%)</t>
         </is>
       </c>
     </row>
@@ -31378,7 +33250,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 983,544/994,533 (98.9%)</t>
+          <t>비영 997,279/1,008,268 (98.9%)</t>
         </is>
       </c>
     </row>
@@ -31426,7 +33298,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 983,542/994,533 (98.9%)</t>
+          <t>비영 997,277/1,008,268 (98.9%)</t>
         </is>
       </c>
     </row>
@@ -31474,7 +33346,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 985,100/994,533 (99.1%)</t>
+          <t>비영 998,835/1,008,268 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -31522,7 +33394,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 985,098/994,533 (99.1%)</t>
+          <t>비영 998,833/1,008,268 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -31570,7 +33442,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 827,497/994,533 (83.2%)</t>
+          <t>비영 837,368/1,008,268 (83.1%)</t>
         </is>
       </c>
     </row>
@@ -31618,7 +33490,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 827,495/994,533 (83.2%)</t>
+          <t>비영 837,366/1,008,268 (83.0%)</t>
         </is>
       </c>
     </row>
@@ -31666,7 +33538,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -31714,7 +33586,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -31762,7 +33634,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -31810,7 +33682,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 994,533/994,533 (100%)</t>
+          <t>비영 1,008,268/1,008,268 (100%)</t>
         </is>
       </c>
     </row>
@@ -31830,8 +33702,16 @@
           <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -31840,7 +33720,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -31870,8 +33750,16 @@
           <t>DIM_DATE.YEAR</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -31880,7 +33768,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -31910,8 +33798,16 @@
           <t>DIM_DATE.MONTH</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -31920,7 +33816,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -31950,8 +33846,16 @@
           <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -31960,7 +33864,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -31990,8 +33894,16 @@
           <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -32000,7 +33912,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -32030,8 +33942,16 @@
           <t>DIM_DATE.IS_HOLIDAY</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -32040,7 +33960,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -32098,7 +34018,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32146,7 +34066,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32194,7 +34114,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 8,140,757/8,141,302 (100.0%)</t>
+          <t>비영 8,162,997/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32242,7 +34162,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,951,939/8,141,302 (97.7%)</t>
+          <t>비영 7,973,993/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -32290,7 +34210,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,894,232/8,141,302 (97.0%)</t>
+          <t>비영 7,916,257/8,163,553 (97.0%)</t>
         </is>
       </c>
     </row>
@@ -32338,7 +34258,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -32386,7 +34306,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,951,944/8,141,302 (97.7%)</t>
+          <t>비영 7,973,999/8,163,553 (97.7%)</t>
         </is>
       </c>
     </row>
@@ -32434,7 +34354,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,963,585/8,141,302 (97.8%)</t>
+          <t>비영 7,985,631/8,163,553 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -32482,7 +34402,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 8,141,301/8,141,302 (100.0%)</t>
+          <t>비영 8,163,552/8,163,553 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32530,7 +34450,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -32578,7 +34498,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 8,141,302/8,141,302 (100%)</t>
+          <t>비영 8,163,553/8,163,553 (100%)</t>
         </is>
       </c>
     </row>
@@ -32626,7 +34546,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 4,023/4,023 (100%)</t>
+          <t>비영 4,074/4,074 (100%)</t>
         </is>
       </c>
     </row>
@@ -32674,7 +34594,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 4,022/4,023 (100.0%)</t>
+          <t>비영 4,073/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32722,7 +34642,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 4,023/4,023 (100%)</t>
+          <t>비영 4,074/4,074 (100%)</t>
         </is>
       </c>
     </row>
@@ -32770,7 +34690,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 4,022/4,023 (100.0%)</t>
+          <t>비영 4,073/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32818,7 +34738,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 4,022/4,023 (100.0%)</t>
+          <t>비영 4,073/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32866,7 +34786,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 4,022/4,023 (100.0%)</t>
+          <t>비영 4,073/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32914,7 +34834,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 4,022/4,023 (100.0%)</t>
+          <t>비영 4,073/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -32962,7 +34882,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 4,021/4,023 (100.0%)</t>
+          <t>비영 4,072/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -33010,7 +34930,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>비영 4,021/4,023 (100.0%)</t>
+          <t>비영 4,072/4,074 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -33058,7 +34978,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>전건 NULL (0/4,023)</t>
+          <t>전건 NULL (0/4,074)</t>
         </is>
       </c>
     </row>
@@ -33106,7 +35026,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 3,576/4,023 (88.9%)</t>
+          <t>비영 3,624/4,074 (89.0%)</t>
         </is>
       </c>
     </row>
@@ -33154,7 +35074,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
@@ -33202,7 +35122,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 35,687/37,164 (96.0%)</t>
+          <t>비영 35,860/37,346 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -33250,7 +35170,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 37,164/37,164 (100%)</t>
+          <t>비영 37,346/37,346 (100%)</t>
         </is>
       </c>
     </row>
